--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_UCAM Murcia.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_UCAM Murcia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2188.28</v>
+        <v>2512.4</v>
       </c>
       <c r="C2" t="n">
-        <v>2185.58</v>
+        <v>2508.84</v>
       </c>
       <c r="D2" t="n">
-        <v>115.3469559567712</v>
+        <v>115.4716920967459</v>
       </c>
       <c r="E2" t="n">
-        <v>106.5621025082587</v>
+        <v>107.2607260726073</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5476190476190477</v>
+        <v>0.5449698655540102</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1431259667979651</v>
+        <v>0.1376720901126408</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3134182174338884</v>
+        <v>0.3082133784928027</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2536115569823435</v>
+        <v>0.2531293463143254</v>
       </c>
       <c r="J2" t="n">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="K2" t="n">
-        <v>307</v>
+        <v>359</v>
       </c>
       <c r="L2" t="n">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="M2" t="n">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="N2" t="n">
-        <v>863</v>
+        <v>985</v>
       </c>
       <c r="O2" t="n">
-        <v>1216</v>
+        <v>1384</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6506153023006955</v>
+        <v>0.6416318961520631</v>
       </c>
       <c r="Q2" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="R2" t="n">
-        <v>307</v>
+        <v>367</v>
       </c>
       <c r="S2" t="n">
-        <v>0.164258962011771</v>
+        <v>0.1701437181270283</v>
       </c>
       <c r="T2" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="U2" t="n">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="V2" t="n">
-        <v>0.09256286784376672</v>
+        <v>0.09457579972183588</v>
       </c>
       <c r="W2" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="X2" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1070090957731407</v>
+        <v>0.1066295781177561</v>
       </c>
       <c r="Z2" t="n">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="AA2" t="n">
-        <v>610</v>
+        <v>707</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3263777421080792</v>
+        <v>0.3277700509967548</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.709703947368421</v>
+        <v>0.7117052023121387</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4234527687296417</v>
+        <v>0.4359673024523161</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3583815028901734</v>
+        <v>0.3774509803921569</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.43</v>
+        <v>0.4260869565217391</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3426229508196721</v>
+        <v>0.3323903818953324</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.419407894736842</v>
+        <v>1.423410404624277</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7167630057803468</v>
+        <v>0.7549019607843137</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.092592592592593</v>
+        <v>1.066168623265742</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8787061994609164</v>
+        <v>0.86810551558753</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.959375</v>
+        <v>0.9862637362637363</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.745454545454545</v>
+        <v>1.729323308270677</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.286908077994429</v>
+        <v>1.320707070707071</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.206128133704736</v>
+        <v>5.446969696969697</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.493036211699164</v>
+        <v>6.767676767676767</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.15285714285714</v>
+        <v>78.5125</v>
       </c>
       <c r="C3" t="n">
-        <v>78.05642857142858</v>
+        <v>78.40125</v>
       </c>
       <c r="D3" t="n">
-        <v>115.3469559567712</v>
+        <v>115.4716920967459</v>
       </c>
       <c r="E3" t="n">
-        <v>106.5621025082587</v>
+        <v>107.2607260726073</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5476190476190477</v>
+        <v>0.5449698655540102</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1431259667979651</v>
+        <v>0.1376720901126408</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3134182174338884</v>
+        <v>0.3082133784928027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2536115569823435</v>
+        <v>0.2531293463143254</v>
       </c>
       <c r="J3" t="n">
-        <v>11.64285714285714</v>
+        <v>11.3125</v>
       </c>
       <c r="K3" t="n">
-        <v>10.96428571428571</v>
+        <v>11.21875</v>
       </c>
       <c r="L3" t="n">
-        <v>6.857142857142857</v>
+        <v>7.1875</v>
       </c>
       <c r="M3" t="n">
-        <v>11.82142857142857</v>
+        <v>11.40625</v>
       </c>
       <c r="N3" t="n">
-        <v>30.82142857142857</v>
+        <v>30.78125</v>
       </c>
       <c r="O3" t="n">
-        <v>43.42857142857143</v>
+        <v>43.25</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6506153023006956</v>
+        <v>0.6416318961520631</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.642857142857143</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>10.96428571428571</v>
+        <v>11.46875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.164258962011771</v>
+        <v>0.1701437181270283</v>
       </c>
       <c r="T3" t="n">
-        <v>2.214285714285714</v>
+        <v>2.40625</v>
       </c>
       <c r="U3" t="n">
-        <v>6.178571428571429</v>
+        <v>6.375</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09256286784376673</v>
+        <v>0.09457579972183588</v>
       </c>
       <c r="W3" t="n">
-        <v>3.071428571428572</v>
+        <v>3.0625</v>
       </c>
       <c r="X3" t="n">
-        <v>7.142857142857143</v>
+        <v>7.1875</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1070090957731407</v>
+        <v>0.1066295781177561</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.464285714285714</v>
+        <v>7.34375</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.78571428571428</v>
+        <v>22.09375</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3263777421080792</v>
+        <v>0.3277700509967548</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.709703947368421</v>
+        <v>0.7117052023121387</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4234527687296418</v>
+        <v>0.4359673024523161</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3583815028901734</v>
+        <v>0.3774509803921569</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.43</v>
+        <v>0.4260869565217391</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3426229508196721</v>
+        <v>0.3323903818953324</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.419407894736842</v>
+        <v>1.423410404624277</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7167630057803468</v>
+        <v>0.7549019607843137</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.092592592592593</v>
+        <v>1.066168623265742</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8787061994609164</v>
+        <v>0.86810551558753</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9593749999999999</v>
+        <v>0.9862637362637363</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.745454545454545</v>
+        <v>1.729323308270677</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.286908077994429</v>
+        <v>1.320707070707071</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.206128133704736</v>
+        <v>5.446969696969697</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.493036211699165</v>
+        <v>6.767676767676767</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2182.88</v>
+        <v>2505.28</v>
       </c>
       <c r="C4" t="n">
-        <v>2185.58</v>
+        <v>2508.84</v>
       </c>
       <c r="D4" t="n">
-        <v>106.5621025082587</v>
+        <v>107.2607260726073</v>
       </c>
       <c r="E4" t="n">
-        <v>115.3469559567712</v>
+        <v>115.4716920967459</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5027517886626307</v>
+        <v>0.5016658733936221</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1492429240349494</v>
+        <v>0.1455863253592526</v>
       </c>
       <c r="H4" t="n">
-        <v>0.293036750483559</v>
+        <v>0.2976782752902156</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2762795817281233</v>
+        <v>0.2774869109947644</v>
       </c>
       <c r="J4" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="K4" t="n">
-        <v>296</v>
+        <v>362</v>
       </c>
       <c r="L4" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="M4" t="n">
-        <v>344</v>
+        <v>388</v>
       </c>
       <c r="N4" t="n">
-        <v>881</v>
+        <v>1018</v>
       </c>
       <c r="O4" t="n">
-        <v>1268</v>
+        <v>1461</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6978536048431481</v>
+        <v>0.695383150880533</v>
       </c>
       <c r="Q4" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="R4" t="n">
-        <v>362</v>
+        <v>412</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1992294991744634</v>
+        <v>0.1960970966206568</v>
       </c>
       <c r="T4" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="U4" t="n">
-        <v>239</v>
+        <v>277</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1315354980737479</v>
+        <v>0.1318419800095193</v>
       </c>
       <c r="W4" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="X4" t="n">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07319757842597689</v>
+        <v>0.06949071870537839</v>
       </c>
       <c r="Z4" t="n">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="AA4" t="n">
-        <v>492</v>
+        <v>592</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2707760044028619</v>
+        <v>0.2817705854355069</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.694794952681388</v>
+        <v>0.6967830253251198</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3839779005524862</v>
+        <v>0.3883495145631068</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3430962343096234</v>
+        <v>0.3465703971119133</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3609022556390977</v>
+        <v>0.3698630136986301</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3272357723577236</v>
+        <v>0.3175675675675675</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.389589905362776</v>
+        <v>1.39356605065024</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6861924686192469</v>
+        <v>0.6931407942238267</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.0032</v>
+        <v>0.983739837398374</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8050139275766016</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.976897689768977</v>
+        <v>1.008356545961003</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.614583333333333</v>
+        <v>1.60952380952381</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.150943396226415</v>
+        <v>1.177458033573141</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.897574123989219</v>
+        <v>5.038369304556355</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.048517520215634</v>
+        <v>6.215827338129497</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.96000000000001</v>
+        <v>78.28999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>78.05642857142858</v>
+        <v>78.40125</v>
       </c>
       <c r="D5" t="n">
-        <v>106.5621025082587</v>
+        <v>107.2607260726073</v>
       </c>
       <c r="E5" t="n">
-        <v>115.3469559567712</v>
+        <v>115.4716920967459</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5027517886626307</v>
+        <v>0.5016658733936221</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1492429240349494</v>
+        <v>0.1455863253592526</v>
       </c>
       <c r="H5" t="n">
-        <v>0.293036750483559</v>
+        <v>0.2976782752902156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2762795817281233</v>
+        <v>0.2774869109947644</v>
       </c>
       <c r="J5" t="n">
-        <v>10.32142857142857</v>
+        <v>9.75</v>
       </c>
       <c r="K5" t="n">
-        <v>10.57142857142857</v>
+        <v>11.3125</v>
       </c>
       <c r="L5" t="n">
-        <v>5.535714285714286</v>
+        <v>5.28125</v>
       </c>
       <c r="M5" t="n">
-        <v>12.28571428571429</v>
+        <v>12.125</v>
       </c>
       <c r="N5" t="n">
-        <v>31.46428571428572</v>
+        <v>31.8125</v>
       </c>
       <c r="O5" t="n">
-        <v>45.28571428571428</v>
+        <v>45.65625</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6978536048431481</v>
+        <v>0.695383150880533</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.964285714285714</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>12.92857142857143</v>
+        <v>12.875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1992294991744634</v>
+        <v>0.1960970966206568</v>
       </c>
       <c r="T5" t="n">
-        <v>2.928571428571428</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>8.535714285714286</v>
+        <v>8.65625</v>
       </c>
       <c r="V5" t="n">
-        <v>0.131535498073748</v>
+        <v>0.1318419800095193</v>
       </c>
       <c r="W5" t="n">
-        <v>1.714285714285714</v>
+        <v>1.6875</v>
       </c>
       <c r="X5" t="n">
-        <v>4.75</v>
+        <v>4.5625</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.07319757842597689</v>
+        <v>0.06949071870537839</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.75</v>
+        <v>5.875</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.57142857142857</v>
+        <v>18.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2707760044028619</v>
+        <v>0.2817705854355069</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.694794952681388</v>
+        <v>0.6967830253251198</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3839779005524862</v>
+        <v>0.3883495145631068</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3430962343096234</v>
+        <v>0.3465703971119133</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3609022556390977</v>
+        <v>0.3698630136986301</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3272357723577236</v>
+        <v>0.3175675675675675</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.389589905362776</v>
+        <v>1.39356605065024</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6861924686192468</v>
+        <v>0.6931407942238267</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.0032</v>
+        <v>0.983739837398374</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8050139275766016</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.976897689768977</v>
+        <v>1.008356545961003</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.614583333333333</v>
+        <v>1.60952380952381</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.150943396226415</v>
+        <v>1.177458033573141</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.897574123989218</v>
+        <v>5.038369304556355</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.048517520215633</v>
+        <v>6.215827338129497</v>
       </c>
     </row>
     <row r="7">
@@ -1419,16 +1419,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="D8" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="E8" t="n">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1437,22 +1437,22 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I8" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="J8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K8" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="L8" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N8" t="n">
         <v>11</v>
@@ -1461,58 +1461,58 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R8" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="S8" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="T8" t="n">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="U8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="W8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>169</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>244</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF8" t="n">
         <v>11</v>
       </c>
-      <c r="Y8" t="n">
-        <v>159</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>222</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>31</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>57</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.544</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>8</v>
-      </c>
       <c r="AG8" t="n">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -1534,35 +1534,35 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>481:29</t>
+          <t>527:51</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>277.2</v>
+        <v>303.8</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.67</v>
+        <v>0.675</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.14</v>
+        <v>1.139</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.177</v>
+        <v>0.168</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.396</v>
+        <v>0.38</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.51</v>
+        <v>0.569</v>
       </c>
       <c r="AV8" t="n">
         <v>0.258</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.112</v>
+        <v>0.11</v>
       </c>
       <c r="AX8" t="n">
         <v>0.201</v>
@@ -1578,91 +1578,91 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G9" t="n">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="H9" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I9" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="J9" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
+        <v>11</v>
+      </c>
+      <c r="M9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N9" t="n">
+        <v>16</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>59</v>
+      </c>
+      <c r="R9" t="n">
+        <v>63</v>
+      </c>
+      <c r="S9" t="n">
+        <v>70</v>
+      </c>
+      <c r="T9" t="n">
+        <v>259</v>
+      </c>
+      <c r="U9" t="n">
+        <v>49</v>
+      </c>
+      <c r="V9" t="n">
+        <v>46</v>
+      </c>
+      <c r="W9" t="n">
+        <v>27</v>
+      </c>
+      <c r="X9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>117</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>148</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AB9" t="n">
         <v>10</v>
       </c>
-      <c r="M9" t="n">
-        <v>12</v>
-      </c>
-      <c r="N9" t="n">
-        <v>15</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>57</v>
-      </c>
-      <c r="R9" t="n">
-        <v>51</v>
-      </c>
-      <c r="S9" t="n">
-        <v>63</v>
-      </c>
-      <c r="T9" t="n">
-        <v>221</v>
-      </c>
-      <c r="U9" t="n">
-        <v>44</v>
-      </c>
-      <c r="V9" t="n">
-        <v>43</v>
-      </c>
-      <c r="W9" t="n">
-        <v>19</v>
-      </c>
-      <c r="X9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>97</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>125</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>8</v>
-      </c>
       <c r="AC9" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.242</v>
+        <v>0.25</v>
       </c>
       <c r="AE9" t="n">
         <v>5</v>
@@ -1674,57 +1674,57 @@
         <v>0.227</v>
       </c>
       <c r="AH9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.375</v>
+        <v>0.389</v>
       </c>
       <c r="AK9" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AL9" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.35</v>
+        <v>0.338</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>457:34</t>
+          <t>527:22</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>345.76</v>
+        <v>391.16</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.508</v>
+        <v>0.51</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.554</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.925</v>
+        <v>0.946</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.165</v>
+        <v>0.151</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.244</v>
+        <v>0.242</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.877</v>
+        <v>0.983</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.339</v>
+        <v>0.333</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="AY9" t="n">
         <v>0.065</v>
@@ -1737,22 +1737,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
         <v>17</v>
       </c>
       <c r="G10" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H10" t="n">
         <v>27</v>
@@ -1761,13 +1761,13 @@
         <v>38</v>
       </c>
       <c r="J10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="L10" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M10" t="n">
         <v>19</v>
@@ -1779,25 +1779,25 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="T10" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="U10" t="n">
         <v>19</v>
       </c>
       <c r="V10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W10" t="n">
         <v>10</v>
@@ -1806,13 +1806,13 @@
         <v>7</v>
       </c>
       <c r="Y10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z10" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.703</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AB10" t="n">
         <v>3</v>
@@ -1836,57 +1836,57 @@
         <v>11</v>
       </c>
       <c r="AI10" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.314</v>
+        <v>0.282</v>
       </c>
       <c r="AK10" t="n">
         <v>6</v>
       </c>
       <c r="AL10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.286</v>
+        <v>0.261</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>469:33</t>
+          <t>535:43</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>140.72</v>
+        <v>150.72</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.51</v>
+        <v>0.478</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.952</v>
+        <v>0.902</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.135</v>
+        <v>0.133</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.257</v>
+        <v>0.237</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.316</v>
+        <v>1.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.134</v>
+        <v>0.126</v>
       </c>
       <c r="AW10" t="n">
         <v>0.075</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.229</v>
+        <v>0.226</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="11">
@@ -2055,100 +2055,100 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>32</v>
+      </c>
+      <c r="C12" t="n">
+        <v>573</v>
+      </c>
+      <c r="D12" t="n">
+        <v>133</v>
+      </c>
+      <c r="E12" t="n">
+        <v>256</v>
+      </c>
+      <c r="F12" t="n">
+        <v>71</v>
+      </c>
+      <c r="G12" t="n">
+        <v>187</v>
+      </c>
+      <c r="H12" t="n">
+        <v>94</v>
+      </c>
+      <c r="I12" t="n">
+        <v>117</v>
+      </c>
+      <c r="J12" t="n">
+        <v>138</v>
+      </c>
+      <c r="K12" t="n">
+        <v>45</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" t="n">
+        <v>26</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>58</v>
+      </c>
+      <c r="R12" t="n">
+        <v>46</v>
+      </c>
+      <c r="S12" t="n">
+        <v>119</v>
+      </c>
+      <c r="T12" t="n">
+        <v>555</v>
+      </c>
+      <c r="U12" t="n">
+        <v>62</v>
+      </c>
+      <c r="V12" t="n">
+        <v>54</v>
+      </c>
+      <c r="W12" t="n">
+        <v>45</v>
+      </c>
+      <c r="X12" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>150</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>209</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>49</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="AE12" t="n">
         <v>28</v>
       </c>
-      <c r="C12" t="n">
-        <v>481</v>
-      </c>
-      <c r="D12" t="n">
-        <v>111</v>
-      </c>
-      <c r="E12" t="n">
-        <v>214</v>
-      </c>
-      <c r="F12" t="n">
-        <v>64</v>
-      </c>
-      <c r="G12" t="n">
-        <v>159</v>
-      </c>
-      <c r="H12" t="n">
-        <v>67</v>
-      </c>
-      <c r="I12" t="n">
-        <v>84</v>
-      </c>
-      <c r="J12" t="n">
-        <v>116</v>
-      </c>
-      <c r="K12" t="n">
-        <v>32</v>
-      </c>
-      <c r="L12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M12" t="n">
-        <v>22</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>53</v>
-      </c>
-      <c r="R12" t="n">
-        <v>40</v>
-      </c>
-      <c r="S12" t="n">
-        <v>90</v>
-      </c>
-      <c r="T12" t="n">
-        <v>448</v>
-      </c>
-      <c r="U12" t="n">
-        <v>57</v>
-      </c>
-      <c r="V12" t="n">
-        <v>47</v>
-      </c>
-      <c r="W12" t="n">
-        <v>30</v>
-      </c>
-      <c r="X12" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>115</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>164</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.701</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>25</v>
-      </c>
       <c r="AF12" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.424</v>
+        <v>0.406</v>
       </c>
       <c r="AH12" t="n">
         <v>6</v>
@@ -2160,51 +2160,51 @@
         <v>0.4</v>
       </c>
       <c r="AK12" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="AL12" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.403</v>
+        <v>0.378</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>702:57</t>
+          <t>814:27</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>462.96</v>
+        <v>552.48</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.555</v>
+        <v>0.541</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.587</v>
+        <v>0.579</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.039</v>
+        <v>1.037</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.114</v>
+        <v>0.105</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.18</v>
+        <v>0.212</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.189</v>
+        <v>2.379</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.295</v>
+        <v>0.304</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.05</v>
+        <v>0.059</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.165</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="13">
@@ -2373,79 +2373,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C14" t="n">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E14" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G14" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" t="n">
+        <v>63</v>
+      </c>
+      <c r="I14" t="n">
+        <v>82</v>
+      </c>
+      <c r="J14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>111</v>
+      </c>
+      <c r="L14" t="n">
         <v>17</v>
       </c>
-      <c r="G14" t="n">
-        <v>41</v>
-      </c>
-      <c r="H14" t="n">
-        <v>60</v>
-      </c>
-      <c r="I14" t="n">
-        <v>78</v>
-      </c>
-      <c r="J14" t="n">
-        <v>47</v>
-      </c>
-      <c r="K14" t="n">
-        <v>97</v>
-      </c>
-      <c r="L14" t="n">
-        <v>14</v>
-      </c>
       <c r="M14" t="n">
+        <v>35</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>34</v>
       </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>29</v>
-      </c>
       <c r="Q14" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R14" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="S14" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="T14" t="n">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="U14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="V14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="Z14" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="AA14" t="n">
         <v>0.73</v>
@@ -2454,75 +2454,75 @@
         <v>4</v>
       </c>
       <c r="AC14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.211</v>
+        <v>0.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.727</v>
+        <v>0.75</v>
       </c>
       <c r="AH14" t="n">
         <v>9</v>
       </c>
       <c r="AI14" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.45</v>
+        <v>0.375</v>
       </c>
       <c r="AK14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL14" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.381</v>
+        <v>0.385</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>566:35</t>
+          <t>653:00</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>193.32</v>
+        <v>218.08</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.596</v>
+        <v>0.584</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.654</v>
+        <v>0.641</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.112</v>
+        <v>1.082</v>
       </c>
       <c r="AS14" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.618</v>
+      </c>
+      <c r="AV14" t="n">
         <v>0.15</v>
       </c>
-      <c r="AT14" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.621</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.153</v>
-      </c>
       <c r="AW14" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.186</v>
+        <v>0.182</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="15">
@@ -2532,67 +2532,67 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C15" t="n">
-        <v>198</v>
+        <v>237</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="H15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J15" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="K15" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M15" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="S15" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="T15" t="n">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="U15" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="V15" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="W15" t="n">
         <v>29</v>
@@ -2601,87 +2601,87 @@
         <v>15</v>
       </c>
       <c r="Y15" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="Z15" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.783</v>
+        <v>0.775</v>
       </c>
       <c r="AB15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AE15" t="n">
         <v>4</v>
       </c>
-      <c r="AC15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>3</v>
-      </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.273</v>
+        <v>0.308</v>
       </c>
       <c r="AH15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AI15" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.531</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AL15" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.32</v>
+        <v>0.322</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>501:57</t>
+          <t>593:09</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>179.08</v>
+        <v>215.84</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.584</v>
+        <v>0.586</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.607</v>
+        <v>0.605</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.106</v>
+        <v>1.098</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.089</v>
+        <v>0.093</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.161</v>
+        <v>0.144</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.688</v>
+        <v>2.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.16</v>
+        <v>0.163</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.128</v>
+        <v>0.124</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="16">
@@ -2691,22 +2691,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
         <v>21</v>
@@ -2715,40 +2715,40 @@
         <v>31</v>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R16" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="S16" t="n">
         <v>28</v>
       </c>
       <c r="T16" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
         <v>17</v>
@@ -2760,22 +2760,22 @@
         <v>2</v>
       </c>
       <c r="Y16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Z16" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.655</v>
+        <v>0.65</v>
       </c>
       <c r="AB16" t="n">
         <v>3</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.3</v>
+        <v>0.273</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2790,10 +2790,10 @@
         <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2806,38 +2806,38 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>303:55</t>
+          <t>320:51</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>77.64</v>
+        <v>82.64</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.404</v>
+        <v>0.393</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.474</v>
+        <v>0.462</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.863</v>
+        <v>0.835</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.09</v>
+        <v>0.097</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.368</v>
+        <v>0.344</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.131</v>
+        <v>0.129</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.14</v>
+        <v>0.137</v>
       </c>
       <c r="AY16" t="n">
         <v>0.007</v>
@@ -2850,16 +2850,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C17" t="n">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E17" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2868,82 +2868,82 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I17" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J17" t="n">
+        <v>25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>92</v>
+      </c>
+      <c r="L17" t="n">
+        <v>74</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18</v>
+      </c>
+      <c r="N17" t="n">
+        <v>26</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>24</v>
       </c>
-      <c r="K17" t="n">
-        <v>82</v>
-      </c>
-      <c r="L17" t="n">
-        <v>66</v>
-      </c>
-      <c r="M17" t="n">
-        <v>16</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="Q17" t="n">
         <v>24</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>21</v>
-      </c>
       <c r="R17" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="S17" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="T17" t="n">
-        <v>290</v>
+        <v>339</v>
       </c>
       <c r="U17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V17" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="W17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="Z17" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.667</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AC17" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.432</v>
+        <v>0.465</v>
       </c>
       <c r="AE17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.4</v>
+        <v>0.455</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -2965,41 +2965,41 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>535:34</t>
+          <t>616:29</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>168.52</v>
+        <v>190.6</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.549</v>
+        <v>0.58</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.586</v>
+        <v>0.615</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.027</v>
+        <v>1.076</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.32</v>
+        <v>0.326</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.143</v>
+        <v>1.042</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.141</v>
+        <v>0.139</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.136</v>
+        <v>0.131</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.167</v>
+        <v>0.16</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="18">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>4</v>
@@ -3327,16 +3327,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3345,83 +3345,83 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
         <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
         <v>4</v>
       </c>
       <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>26</v>
+      </c>
+      <c r="S20" t="n">
+        <v>18</v>
+      </c>
+      <c r="T20" t="n">
+        <v>52</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>12</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="AB20" t="n">
         <v>3</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>18</v>
-      </c>
-      <c r="S20" t="n">
-        <v>12</v>
-      </c>
-      <c r="T20" t="n">
-        <v>41</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AF20" t="n">
         <v>5</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AG20" t="n">
         <v>0.2</v>
       </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
       <c r="AH20" t="n">
         <v>0</v>
       </c>
@@ -3442,38 +3442,38 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>97:51</t>
+          <t>132:29</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>26.6</v>
+        <v>36.24</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.588</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.678</v>
+        <v>0.651</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.203</v>
+        <v>1.159</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.706</v>
+        <v>0.696</v>
       </c>
       <c r="AU20" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.122</v>
+        <v>0.123</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.079</v>
+        <v>0.074</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.122</v>
+        <v>0.129</v>
       </c>
       <c r="AY20" t="n">
         <v>0.003</v>
@@ -3632,7 +3632,7 @@
         <v>0.045</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -3645,40 +3645,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C22" t="n">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E22" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="H22" t="n">
+        <v>16</v>
+      </c>
+      <c r="I22" t="n">
+        <v>20</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>30</v>
+      </c>
+      <c r="L22" t="n">
         <v>7</v>
       </c>
-      <c r="I22" t="n">
-        <v>9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>5</v>
-      </c>
-      <c r="K22" t="n">
-        <v>21</v>
-      </c>
-      <c r="L22" t="n">
-        <v>4</v>
-      </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N22" t="n">
         <v>4</v>
@@ -3687,111 +3687,111 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>15</v>
+      </c>
+      <c r="R22" t="n">
+        <v>31</v>
+      </c>
+      <c r="S22" t="n">
+        <v>16</v>
+      </c>
+      <c r="T22" t="n">
+        <v>113</v>
+      </c>
+      <c r="U22" t="n">
+        <v>13</v>
+      </c>
+      <c r="V22" t="n">
+        <v>19</v>
+      </c>
+      <c r="W22" t="n">
         <v>11</v>
       </c>
-      <c r="Q22" t="n">
-        <v>11</v>
-      </c>
-      <c r="R22" t="n">
+      <c r="X22" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y22" t="n">
         <v>24</v>
       </c>
-      <c r="S22" t="n">
+      <c r="Z22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AE22" t="n">
         <v>8</v>
       </c>
-      <c r="T22" t="n">
-        <v>78</v>
-      </c>
-      <c r="U22" t="n">
+      <c r="AF22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AH22" t="n">
         <v>10</v>
       </c>
-      <c r="V22" t="n">
-        <v>14</v>
-      </c>
-      <c r="W22" t="n">
-        <v>6</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>8</v>
-      </c>
       <c r="AI22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AK22" t="n">
         <v>19</v>
       </c>
-      <c r="AJ22" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>15</v>
-      </c>
       <c r="AL22" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.556</v>
+        <v>0.487</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>214:16</t>
+          <t>292:34</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>91.95999999999999</v>
+        <v>132.8</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.643</v>
+        <v>0.61</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.655</v>
+        <v>0.632</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.153</v>
+        <v>1.122</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.12</v>
+        <v>0.113</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.091</v>
+        <v>0.147</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.455</v>
+        <v>0.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.192</v>
+        <v>0.204</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.021</v>
+        <v>0.026</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.107</v>
+        <v>0.11</v>
       </c>
       <c r="AY22" t="n">
         <v>0.006</v>
@@ -3950,10 +3950,10 @@
         <v>0.034</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.116</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="24">
@@ -3963,156 +3963,156 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>47</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>21</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>13</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4</v>
+      </c>
+      <c r="N24" t="n">
         <v>2</v>
       </c>
-      <c r="C24" t="n">
-        <v>12</v>
-      </c>
-      <c r="D24" t="n">
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>11</v>
+      </c>
+      <c r="S24" t="n">
+        <v>8</v>
+      </c>
+      <c r="T24" t="n">
+        <v>36</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5</v>
+      </c>
+      <c r="W24" t="n">
         <v>4</v>
       </c>
-      <c r="E24" t="n">
-        <v>7</v>
-      </c>
-      <c r="F24" t="n">
+      <c r="X24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" t="n">
-        <v>7</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="AF24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>1</v>
       </c>
-      <c r="I24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>2</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z24" t="n">
+      <c r="AK24" t="n">
         <v>6</v>
       </c>
-      <c r="AA24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1</v>
-      </c>
       <c r="AL24" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.143</v>
+        <v>0.316</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>27:04</t>
+          <t>89:38</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>17.88</v>
+        <v>51.64</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.393</v>
+        <v>0.512</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.403</v>
+        <v>0.538</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.671</v>
+        <v>0.91</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.168</v>
+        <v>0.155</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="AU24" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.296</v>
+        <v>0.258</v>
       </c>
       <c r="AW24" t="n">
         <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.161</v>
+        <v>0.155</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="25">
@@ -4122,40 +4122,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C25" t="n">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G25" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="H25" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I25" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J25" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K25" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N25" t="n">
         <v>8</v>
@@ -4164,25 +4164,25 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R25" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="S25" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="T25" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="U25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W25" t="n">
         <v>15</v>
@@ -4191,87 +4191,87 @@
         <v>7</v>
       </c>
       <c r="Y25" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="Z25" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.833</v>
+        <v>0.845</v>
       </c>
       <c r="AB25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AE25" t="n">
         <v>2</v>
       </c>
-      <c r="AC25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
       <c r="AF25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.167</v>
+        <v>0.286</v>
       </c>
       <c r="AH25" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AI25" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.412</v>
+        <v>0.45</v>
       </c>
       <c r="AK25" t="n">
         <v>23</v>
       </c>
       <c r="AL25" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.397</v>
+        <v>0.343</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>527:49</t>
+          <t>608:56</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>148.28</v>
+        <v>169.04</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.596</v>
+        <v>0.576</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.642</v>
+        <v>0.625</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.18</v>
+        <v>1.154</v>
       </c>
       <c r="AS25" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.231</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AX25" t="n">
         <v>0.081</v>
       </c>
-      <c r="AT25" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0.082</v>
-      </c>
       <c r="AY25" t="n">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="26">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -4308,10 +4308,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="L26" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4323,13 +4323,13 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -4436,157 +4436,157 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2897</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>676</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1220</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>937</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>546</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>735</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>847</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>759</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>702</v>
       </c>
       <c r="T27" t="n">
-        <v>62</v>
+        <v>3223</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>362</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>985</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>0.712</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>0.436</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>0.377</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.426</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>707</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.332</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>6450:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>28</v>
+        <v>2876.4</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.007</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>0.253</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.321</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4595,157 +4595,157 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C28" t="n">
-        <v>2521</v>
+        <v>2691</v>
       </c>
       <c r="D28" t="n">
-        <v>581</v>
+        <v>691</v>
       </c>
       <c r="E28" t="n">
-        <v>1059</v>
+        <v>1363</v>
       </c>
       <c r="F28" t="n">
-        <v>295</v>
+        <v>242</v>
       </c>
       <c r="G28" t="n">
-        <v>810</v>
+        <v>738</v>
       </c>
       <c r="H28" t="n">
-        <v>474</v>
+        <v>583</v>
       </c>
       <c r="I28" t="n">
-        <v>637</v>
+        <v>787</v>
       </c>
       <c r="J28" t="n">
-        <v>462</v>
+        <v>491</v>
       </c>
       <c r="K28" t="n">
-        <v>731</v>
+        <v>817</v>
       </c>
       <c r="L28" t="n">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="M28" t="n">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="N28" t="n">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>359</v>
+        <v>417</v>
       </c>
       <c r="Q28" t="n">
-        <v>331</v>
+        <v>388</v>
       </c>
       <c r="R28" t="n">
-        <v>658</v>
+        <v>717</v>
       </c>
       <c r="S28" t="n">
-        <v>605</v>
+        <v>756</v>
       </c>
       <c r="T28" t="n">
-        <v>2806</v>
+        <v>2949</v>
       </c>
       <c r="U28" t="n">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="V28" t="n">
-        <v>307</v>
+        <v>362</v>
       </c>
       <c r="W28" t="n">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="X28" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="Y28" t="n">
-        <v>863</v>
+        <v>1018</v>
       </c>
       <c r="Z28" t="n">
-        <v>1216</v>
+        <v>1461</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.71</v>
+        <v>0.697</v>
       </c>
       <c r="AB28" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AC28" t="n">
-        <v>307</v>
+        <v>412</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.423</v>
+        <v>0.388</v>
       </c>
       <c r="AE28" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="AF28" t="n">
-        <v>173</v>
+        <v>277</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.358</v>
+        <v>0.347</v>
       </c>
       <c r="AH28" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="AI28" t="n">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="AK28" t="n">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="AL28" t="n">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.343</v>
+        <v>0.318</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>5625:00</t>
+          <t>6450:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>2508.28</v>
+        <v>2864.28</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.548</v>
+        <v>0.502</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.586</v>
+        <v>0.55</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.005</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.143</v>
+        <v>0.146</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.254</v>
+        <v>0.277</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.287</v>
+        <v>1.177</v>
       </c>
       <c r="AV28" t="n">
         <v>0.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.141</v>
+        <v>0.138</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -4754,1667 +4754,1667 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" t="n">
-        <v>2329</v>
-      </c>
-      <c r="D29" t="n">
-        <v>600</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1192</v>
-      </c>
-      <c r="F29" t="n">
-        <v>209</v>
-      </c>
-      <c r="G29" t="n">
-        <v>625</v>
-      </c>
-      <c r="H29" t="n">
-        <v>502</v>
-      </c>
-      <c r="I29" t="n">
-        <v>677</v>
-      </c>
-      <c r="J29" t="n">
-        <v>427</v>
-      </c>
-      <c r="K29" t="n">
-        <v>701</v>
-      </c>
-      <c r="L29" t="n">
-        <v>303</v>
-      </c>
-      <c r="M29" t="n">
-        <v>173</v>
-      </c>
-      <c r="N29" t="n">
-        <v>128</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>371</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>344</v>
-      </c>
-      <c r="R29" t="n">
-        <v>620</v>
-      </c>
-      <c r="S29" t="n">
-        <v>656</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2543</v>
-      </c>
-      <c r="U29" t="n">
-        <v>289</v>
-      </c>
-      <c r="V29" t="n">
-        <v>296</v>
-      </c>
-      <c r="W29" t="n">
-        <v>155</v>
-      </c>
-      <c r="X29" t="n">
-        <v>96</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>881</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1268</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>139</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>362</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.384</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>82</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>239</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>133</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>161</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>492</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>5625:00</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>2485.88</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0.9370000000000001</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1.151</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
+          <t>#0 D. CACOK (Per Game)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>30</v>
+      </c>
+      <c r="C30" t="n">
+        <v>11.533</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.533</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.767</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3.767</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T30" t="n">
+        <v>405</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.867</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>5.633</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>8.132999999999999</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AO30" t="n">
+        <v>10.127</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.036</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#0 D. CACOK (Per Game)</t>
+          <t>#1 M. FORREST (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>11.704</v>
+        <v>11.562</v>
       </c>
       <c r="D31" t="n">
-        <v>4.519</v>
+        <v>1.906</v>
       </c>
       <c r="E31" t="n">
-        <v>6.741</v>
+        <v>3.781</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.844</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>5.375</v>
       </c>
       <c r="H31" t="n">
-        <v>2.667</v>
+        <v>2.219</v>
       </c>
       <c r="I31" t="n">
-        <v>3.889</v>
+        <v>2.781</v>
       </c>
       <c r="J31" t="n">
-        <v>0.926</v>
+        <v>1.812</v>
       </c>
       <c r="K31" t="n">
-        <v>3.296</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.815</v>
+        <v>0.344</v>
       </c>
       <c r="M31" t="n">
-        <v>0.741</v>
+        <v>0.469</v>
       </c>
       <c r="N31" t="n">
-        <v>0.407</v>
+        <v>0.5</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.815</v>
+        <v>1.844</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.815</v>
+        <v>1.844</v>
       </c>
       <c r="R31" t="n">
-        <v>3.741</v>
+        <v>1.969</v>
       </c>
       <c r="S31" t="n">
-        <v>3.778</v>
+        <v>2.188</v>
       </c>
       <c r="T31" t="n">
-        <v>369</v>
+        <v>259</v>
       </c>
       <c r="U31" t="n">
-        <v>1.63</v>
+        <v>1.531</v>
       </c>
       <c r="V31" t="n">
-        <v>1.778</v>
+        <v>1.438</v>
       </c>
       <c r="W31" t="n">
-        <v>0.556</v>
+        <v>0.844</v>
       </c>
       <c r="X31" t="n">
-        <v>0.407</v>
+        <v>0.469</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.889</v>
+        <v>3.656</v>
       </c>
       <c r="Z31" t="n">
-        <v>8.222</v>
+        <v>4.625</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.716</v>
+        <v>0.791</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.148</v>
+        <v>0.312</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.111</v>
+        <v>1.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.544</v>
+        <v>0.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.148</v>
+        <v>0.156</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.296</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.5</v>
+        <v>0.227</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>0.389</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.625</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>4.812</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>0.338</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>10.267</v>
+        <v>12.224</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.14</v>
+        <v>0.946</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.177</v>
+        <v>0.151</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.396</v>
+        <v>0.242</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.51</v>
+        <v>0.983</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.258</v>
+        <v>0.333</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.112</v>
+        <v>0.023</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.201</v>
+        <v>0.065</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.035</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#1 M. FORREST (Per Game)</t>
+          <t>#2 S. RAIESTE (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32" t="n">
-        <v>11.429</v>
+        <v>5.037</v>
       </c>
       <c r="D32" t="n">
-        <v>1.714</v>
+        <v>1.074</v>
       </c>
       <c r="E32" t="n">
-        <v>3.607</v>
+        <v>1.926</v>
       </c>
       <c r="F32" t="n">
-        <v>1.929</v>
+        <v>0.63</v>
       </c>
       <c r="G32" t="n">
-        <v>5.464</v>
+        <v>2.296</v>
       </c>
       <c r="H32" t="n">
-        <v>2.214</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>2.821</v>
+        <v>1.407</v>
       </c>
       <c r="J32" t="n">
-        <v>1.786</v>
+        <v>0.963</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>4.185</v>
       </c>
       <c r="L32" t="n">
-        <v>0.357</v>
+        <v>1.37</v>
       </c>
       <c r="M32" t="n">
-        <v>0.429</v>
+        <v>0.704</v>
       </c>
       <c r="N32" t="n">
-        <v>0.536</v>
+        <v>0.519</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.036</v>
+        <v>0.741</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.036</v>
+        <v>0.741</v>
       </c>
       <c r="R32" t="n">
-        <v>1.821</v>
+        <v>3.407</v>
       </c>
       <c r="S32" t="n">
-        <v>2.25</v>
+        <v>1.222</v>
       </c>
       <c r="T32" t="n">
-        <v>221</v>
+        <v>187</v>
       </c>
       <c r="U32" t="n">
-        <v>1.571</v>
+        <v>0.704</v>
       </c>
       <c r="V32" t="n">
-        <v>1.536</v>
+        <v>1.111</v>
       </c>
       <c r="W32" t="n">
-        <v>0.679</v>
+        <v>0.37</v>
       </c>
       <c r="X32" t="n">
-        <v>0.357</v>
+        <v>0.259</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.464</v>
+        <v>1.963</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.464</v>
+        <v>2.852</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.776</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.286</v>
+        <v>0.111</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.179</v>
+        <v>0.333</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.242</v>
+        <v>0.333</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.179</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.786</v>
+        <v>0.148</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.227</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.214</v>
+        <v>0.407</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.571</v>
+        <v>1.444</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.375</v>
+        <v>0.282</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.714</v>
+        <v>0.222</v>
       </c>
       <c r="AL32" t="n">
-        <v>4.893</v>
+        <v>0.852</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.35</v>
+        <v>0.261</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>12.349</v>
+        <v>5.582</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.508</v>
+        <v>0.478</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.554</v>
+        <v>0.52</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.925</v>
+        <v>0.902</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.165</v>
+        <v>0.133</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.244</v>
+        <v>0.237</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.877</v>
+        <v>1.3</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.339</v>
+        <v>0.126</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.024</v>
+        <v>0.075</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.067</v>
+        <v>0.226</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.065</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#2 S. RAIESTE (Per Game)</t>
+          <t>#3 J. MARTÍNEZ (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>5.826</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1.217</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.739</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>2.435</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.174</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1.652</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1.087</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>4.304</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1.391</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.826</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0.609</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.826</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.826</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.478</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.304</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0.826</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.217</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.261</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.217</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.703</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.478</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.522</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.314</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.261</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.913</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>00:19</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.118</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.952</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.135</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.257</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.316</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.134</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.229</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#3 J. MARTÍNEZ (Per Game)</t>
+          <t>#5 D. DEJULIUS (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>17.906</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>4.156</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>2.219</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>5.844</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2.938</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>3.656</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>4.312</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1.406</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.812</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1.812</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.438</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.719</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.938</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.688</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.406</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>0.844</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>4.688</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>6.531</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>0.718</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.531</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.969</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>0.516</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.156</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.031</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>5.375</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>00:19</t>
+          <t>25:27</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>17.265</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>0.541</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.037</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>0.212</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.379</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>0.304</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#5 D. DEJULIUS (Per Game)</t>
+          <t>#6 D. GARCÍA (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>17.179</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>3.964</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>7.643</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>2.286</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>5.679</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.393</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>4.143</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1.143</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.786</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.893</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.893</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.429</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.214</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.036</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.679</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.071</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.607</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>4.107</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.857</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.701</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.357</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.679</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.507</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.893</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.107</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.424</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.536</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.071</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>5.143</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.403</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>25:06</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>16.534</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.555</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.039</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.114</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.189</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.295</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#6 D. GARCÍA (Per Game)</t>
+          <t>#8 H. SANT-ROOS (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>7.375</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1.812</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>3.062</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.594</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1.562</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1.969</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>2.562</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1.719</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>3.469</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1.094</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.062</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.062</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.531</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.219</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.969</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.594</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>3.375</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>4.625</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>6.815</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>0.641</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.082</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>0.426</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>1.618</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#8 H. SANT-ROOS (Per Game)</t>
+          <t>#12 J. RADEBAUGH (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C37" t="n">
-        <v>7.679</v>
+        <v>8.172000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>1.857</v>
+        <v>1.31</v>
       </c>
       <c r="E37" t="n">
-        <v>3.179</v>
+        <v>2.103</v>
       </c>
       <c r="F37" t="n">
-        <v>0.607</v>
+        <v>1.552</v>
       </c>
       <c r="G37" t="n">
-        <v>1.464</v>
+        <v>4.103</v>
       </c>
       <c r="H37" t="n">
-        <v>2.143</v>
+        <v>0.897</v>
       </c>
       <c r="I37" t="n">
-        <v>2.786</v>
+        <v>1.241</v>
       </c>
       <c r="J37" t="n">
-        <v>1.679</v>
+        <v>1.724</v>
       </c>
       <c r="K37" t="n">
-        <v>3.464</v>
+        <v>2.379</v>
       </c>
       <c r="L37" t="n">
-        <v>0.5</v>
+        <v>0.448</v>
       </c>
       <c r="M37" t="n">
-        <v>1.214</v>
+        <v>0.966</v>
       </c>
       <c r="N37" t="n">
-        <v>0.179</v>
+        <v>0.517</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.036</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.036</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R37" t="n">
-        <v>1.536</v>
+        <v>2.31</v>
       </c>
       <c r="S37" t="n">
-        <v>2.393</v>
+        <v>1.621</v>
       </c>
       <c r="T37" t="n">
-        <v>328</v>
+        <v>265</v>
       </c>
       <c r="U37" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="W37" t="n">
         <v>1</v>
       </c>
-      <c r="V37" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.036</v>
-      </c>
       <c r="X37" t="n">
-        <v>0.643</v>
+        <v>0.517</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.571</v>
+        <v>1.897</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.893</v>
+        <v>2.448</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.73</v>
+        <v>0.775</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.143</v>
+        <v>0.172</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.679</v>
+        <v>0.448</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.211</v>
+        <v>0.385</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.286</v>
+        <v>0.138</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.393</v>
+        <v>0.448</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.727</v>
+        <v>0.308</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.321</v>
+        <v>0.586</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.714</v>
+        <v>1.103</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.45</v>
+        <v>0.531</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.286</v>
+        <v>0.966</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.75</v>
+        <v>3</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.381</v>
+        <v>0.322</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>6.904</v>
+        <v>7.443</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.596</v>
+        <v>0.586</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.654</v>
+        <v>0.605</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.112</v>
+        <v>1.098</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.15</v>
+        <v>0.093</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.462</v>
+        <v>0.144</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.621</v>
+        <v>2.5</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.153</v>
+        <v>0.163</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.186</v>
+        <v>0.124</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#12 J. RADEBAUGH (Per Game)</t>
+          <t>#13 W. FALK (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C38" t="n">
-        <v>7.92</v>
+        <v>2.3</v>
       </c>
       <c r="D38" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="E38" t="n">
-        <v>1.96</v>
+        <v>1.367</v>
       </c>
       <c r="F38" t="n">
-        <v>1.52</v>
+        <v>0.067</v>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>0.667</v>
       </c>
       <c r="H38" t="n">
-        <v>0.96</v>
+        <v>0.7</v>
       </c>
       <c r="I38" t="n">
-        <v>1.28</v>
+        <v>1.033</v>
       </c>
       <c r="J38" t="n">
-        <v>1.72</v>
+        <v>0.233</v>
       </c>
       <c r="K38" t="n">
-        <v>2.36</v>
+        <v>1.367</v>
       </c>
       <c r="L38" t="n">
-        <v>0.36</v>
+        <v>1.267</v>
       </c>
       <c r="M38" t="n">
-        <v>0.96</v>
+        <v>0.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.64</v>
+        <v>0.267</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.64</v>
+        <v>0.267</v>
       </c>
       <c r="R38" t="n">
-        <v>2.16</v>
+        <v>1.933</v>
       </c>
       <c r="S38" t="n">
-        <v>1.64</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="T38" t="n">
-        <v>226</v>
+        <v>90</v>
       </c>
       <c r="U38" t="n">
-        <v>1.12</v>
+        <v>0.167</v>
       </c>
       <c r="V38" t="n">
-        <v>0.48</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="W38" t="n">
-        <v>1.16</v>
+        <v>0.133</v>
       </c>
       <c r="X38" t="n">
-        <v>0.6</v>
+        <v>0.067</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.88</v>
+        <v>1.3</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.783</v>
+        <v>0.65</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="AC38" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
         <v>0.4</v>
       </c>
-      <c r="AD38" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>3</v>
-      </c>
       <c r="AM38" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>7.163</v>
+        <v>2.755</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.584</v>
+        <v>0.393</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.607</v>
+        <v>0.462</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.106</v>
+        <v>0.835</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.089</v>
+        <v>0.097</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.161</v>
+        <v>0.344</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.688</v>
+        <v>0.875</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.16</v>
+        <v>0.116</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.02</v>
+        <v>0.129</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.128</v>
+        <v>0.137</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.06</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#13 W. FALK (Per Game)</t>
+          <t>#15 E. CATE (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C39" t="n">
-        <v>2.393</v>
+        <v>6.406</v>
       </c>
       <c r="D39" t="n">
-        <v>0.714</v>
+        <v>2.5</v>
       </c>
       <c r="E39" t="n">
-        <v>1.357</v>
+        <v>4.312</v>
       </c>
       <c r="F39" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.679</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.031</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2.312</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>0.75</v>
       </c>
-      <c r="I39" t="n">
-        <v>1.107</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1.393</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.286</v>
-      </c>
-      <c r="M39" t="n">
+      <c r="Q39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.188</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.219</v>
+      </c>
+      <c r="T39" t="n">
+        <v>339</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W39" t="n">
         <v>0.25</v>
       </c>
-      <c r="N39" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.964</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1</v>
-      </c>
-      <c r="T39" t="n">
-        <v>86</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0.143</v>
-      </c>
       <c r="X39" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.357</v>
+        <v>2.969</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.071</v>
+        <v>4.312</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.655</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.107</v>
+        <v>0.625</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.357</v>
+        <v>1.344</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.3</v>
+        <v>0.465</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.036</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
         <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
         <v>0</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>2.773</v>
+        <v>5.956</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.404</v>
+        <v>0.58</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.474</v>
+        <v>0.615</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.863</v>
+        <v>1.076</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.09</v>
+        <v>0.126</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.368</v>
+        <v>0.326</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.857</v>
+        <v>1.042</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.115</v>
+        <v>0.139</v>
       </c>
       <c r="AW39" t="n">
         <v>0.131</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.007</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#15 E. CATE (Per Game)</t>
+          <t>#16 R. LÓPEZ (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C40" t="n">
-        <v>6.179</v>
+        <v>0.308</v>
       </c>
       <c r="D40" t="n">
-        <v>2.393</v>
+        <v>0.154</v>
       </c>
       <c r="E40" t="n">
-        <v>4.357</v>
+        <v>0.154</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -6423,82 +6423,82 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.393</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>2.071</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2.929</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>2.357</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.75</v>
+        <v>0.231</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.75</v>
+        <v>0.231</v>
       </c>
       <c r="R40" t="n">
-        <v>2.179</v>
+        <v>0.308</v>
       </c>
       <c r="S40" t="n">
-        <v>2.179</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>290</v>
+        <v>-3</v>
       </c>
       <c r="U40" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.107</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.929</v>
+        <v>0.154</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.393</v>
+        <v>0.154</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.321</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.432</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
         <v>0</v>
@@ -6520,60 +6520,60 @@
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>01:01</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>6.019</v>
+        <v>0.385</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.549</v>
+        <v>1</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.586</v>
+        <v>1</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.027</v>
+        <v>0.8</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.125</v>
+        <v>0.6</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.143</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.141</v>
+        <v>0.168</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.136</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#16 R. LÓPEZ (Per Game)</t>
+          <t>#20 P. SEVILLA (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -6606,19 +6606,19 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -6633,13 +6633,13 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
@@ -6679,23 +6679,23 @@
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>01:20</t>
+          <t>03:18</t>
         </is>
       </c>
       <c r="AO41" t="n">
         <v>0.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
         <v>0</v>
@@ -6704,7 +6704,7 @@
         <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.168</v>
+        <v>0.068</v>
       </c>
       <c r="AW41" t="n">
         <v>0</v>
@@ -6719,20 +6719,20 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#20 P. SEVILLA (Per Game)</t>
+          <t>#21 M. DIAGNÉ (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1.615</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5</v>
+        <v>0.885</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -6741,49 +6741,49 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="T42" t="n">
-        <v>-1</v>
+        <v>52</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -6792,31 +6792,31 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.5</v>
+        <v>1.231</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>0.781</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH42" t="n">
         <v>0</v>
@@ -6838,1151 +6838,1151 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>03:18</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>0.5</v>
+        <v>1.394</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>0.651</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.159</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>0.696</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.068</v>
+        <v>0.123</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#21 M. DIAGNÉ (Per Game)</t>
+          <t>#24 Z. HICKS (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C43" t="n">
-        <v>1.455</v>
+        <v>1.8</v>
       </c>
       <c r="D43" t="n">
-        <v>0.455</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0.773</v>
+        <v>0.133</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>0.533</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1.867</v>
       </c>
       <c r="H43" t="n">
-        <v>0.545</v>
+        <v>0.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.333</v>
       </c>
       <c r="J43" t="n">
-        <v>0.136</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="T43" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA43" t="n">
         <v>0.5</v>
       </c>
-      <c r="L43" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="T43" t="n">
-        <v>41</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.091</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0.875</v>
-      </c>
       <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="AO43" t="n">
+        <v>2.413</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="AW43" t="n">
         <v>0.045</v>
       </c>
-      <c r="AC43" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>04:26</t>
-        </is>
-      </c>
-      <c r="AO43" t="n">
-        <v>1.209</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>1.203</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>0.079</v>
-      </c>
       <c r="AX43" t="n">
-        <v>0.122</v>
+        <v>0.114</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#24 Z. HICKS (Per Game)</t>
+          <t>#30 K. MARTIN (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C44" t="n">
-        <v>1.8</v>
+        <v>8.765000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1.353</v>
       </c>
       <c r="E44" t="n">
-        <v>0.133</v>
+        <v>2.765</v>
       </c>
       <c r="F44" t="n">
-        <v>0.533</v>
+        <v>1.706</v>
       </c>
       <c r="G44" t="n">
-        <v>1.867</v>
+        <v>3.647</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>0.333</v>
+        <v>1.176</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="K44" t="n">
-        <v>0.867</v>
+        <v>1.765</v>
       </c>
       <c r="L44" t="n">
-        <v>0.333</v>
+        <v>0.412</v>
       </c>
       <c r="M44" t="n">
-        <v>0.067</v>
+        <v>0.471</v>
       </c>
       <c r="N44" t="n">
-        <v>0.067</v>
+        <v>0.235</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.267</v>
+        <v>0.882</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.267</v>
+        <v>0.882</v>
       </c>
       <c r="R44" t="n">
-        <v>1.6</v>
+        <v>1.824</v>
       </c>
       <c r="S44" t="n">
-        <v>0.133</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="T44" t="n">
-        <v>-3</v>
+        <v>113</v>
       </c>
       <c r="U44" t="n">
-        <v>0.2</v>
+        <v>0.765</v>
       </c>
       <c r="V44" t="n">
-        <v>0.2</v>
+        <v>1.118</v>
       </c>
       <c r="W44" t="n">
-        <v>0.2</v>
+        <v>0.647</v>
       </c>
       <c r="X44" t="n">
-        <v>0.067</v>
+        <v>0.412</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.2</v>
+        <v>1.412</v>
       </c>
       <c r="Z44" t="n">
+        <v>1.882</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>2.294</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AO44" t="n">
+        <v>7.812</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AU44" t="n">
         <v>0.4</v>
       </c>
-      <c r="AA44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1.267</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="AO44" t="n">
-        <v>2.413</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0.746</v>
-      </c>
-      <c r="AS44" t="n">
+      <c r="AV44" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="AX44" t="n">
         <v>0.11</v>
       </c>
-      <c r="AT44" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0.116</v>
-      </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#30 K. MARTIN (Per Game)</t>
+          <t>#31 D. ENNIS (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C45" t="n">
-        <v>8.154</v>
+        <v>10.44</v>
       </c>
       <c r="D45" t="n">
-        <v>1.154</v>
+        <v>2.24</v>
       </c>
       <c r="E45" t="n">
-        <v>2.385</v>
+        <v>5.08</v>
       </c>
       <c r="F45" t="n">
-        <v>1.769</v>
+        <v>1.36</v>
       </c>
       <c r="G45" t="n">
-        <v>3.538</v>
+        <v>4.36</v>
       </c>
       <c r="H45" t="n">
-        <v>0.538</v>
+        <v>1.88</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6919999999999999</v>
+        <v>2.56</v>
       </c>
       <c r="J45" t="n">
-        <v>0.385</v>
+        <v>3.64</v>
       </c>
       <c r="K45" t="n">
-        <v>1.615</v>
+        <v>2.4</v>
       </c>
       <c r="L45" t="n">
-        <v>0.308</v>
+        <v>0.76</v>
       </c>
       <c r="M45" t="n">
-        <v>0.462</v>
+        <v>1.08</v>
       </c>
       <c r="N45" t="n">
-        <v>0.308</v>
+        <v>0.68</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.846</v>
+        <v>1.76</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.846</v>
+        <v>1.76</v>
       </c>
       <c r="R45" t="n">
-        <v>1.846</v>
+        <v>1.76</v>
       </c>
       <c r="S45" t="n">
-        <v>0.615</v>
+        <v>2.6</v>
       </c>
       <c r="T45" t="n">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="U45" t="n">
-        <v>0.769</v>
+        <v>1.72</v>
       </c>
       <c r="V45" t="n">
-        <v>1.077</v>
+        <v>0.96</v>
       </c>
       <c r="W45" t="n">
-        <v>0.462</v>
+        <v>0.96</v>
       </c>
       <c r="X45" t="n">
-        <v>0.308</v>
+        <v>0.52</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.923</v>
+        <v>3.48</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.308</v>
+        <v>5.72</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.706</v>
+        <v>0.608</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.385</v>
+        <v>0.52</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.6919999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.556</v>
+        <v>0.371</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.385</v>
+        <v>0.12</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.077</v>
+        <v>0.52</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.357</v>
+        <v>0.231</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.615</v>
+        <v>0.48</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.462</v>
+        <v>0.8</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.421</v>
+        <v>0.6</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.154</v>
+        <v>0.88</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.077</v>
+        <v>3.56</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.556</v>
+        <v>0.247</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>24:30</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>7.074</v>
+        <v>12.326</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.643</v>
+        <v>0.453</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.655</v>
+        <v>0.494</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.153</v>
+        <v>0.847</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.12</v>
+        <v>0.143</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.091</v>
+        <v>0.199</v>
       </c>
       <c r="AU45" t="n">
-        <v>0.455</v>
+        <v>2.068</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.192</v>
+        <v>0.226</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.021</v>
+        <v>0.034</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.014</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#31 D. ENNIS (Per Game)</t>
+          <t>#50 J. HANDS (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C46" t="n">
-        <v>10.44</v>
+        <v>7.833</v>
       </c>
       <c r="D46" t="n">
-        <v>2.24</v>
+        <v>1.5</v>
       </c>
       <c r="E46" t="n">
-        <v>5.08</v>
+        <v>3.333</v>
       </c>
       <c r="F46" t="n">
-        <v>1.36</v>
+        <v>1.333</v>
       </c>
       <c r="G46" t="n">
-        <v>4.36</v>
+        <v>3.5</v>
       </c>
       <c r="H46" t="n">
-        <v>1.88</v>
+        <v>0.833</v>
       </c>
       <c r="I46" t="n">
-        <v>2.56</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>3.64</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>2.4</v>
+        <v>2.167</v>
       </c>
       <c r="L46" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.08</v>
+        <v>0.667</v>
       </c>
       <c r="N46" t="n">
-        <v>0.68</v>
+        <v>0.333</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.76</v>
+        <v>1.333</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.76</v>
+        <v>1.333</v>
       </c>
       <c r="R46" t="n">
-        <v>1.76</v>
+        <v>1.833</v>
       </c>
       <c r="S46" t="n">
-        <v>2.6</v>
+        <v>1.333</v>
       </c>
       <c r="T46" t="n">
-        <v>289</v>
+        <v>36</v>
       </c>
       <c r="U46" t="n">
-        <v>1.72</v>
+        <v>0.333</v>
       </c>
       <c r="V46" t="n">
-        <v>0.96</v>
+        <v>0.833</v>
       </c>
       <c r="W46" t="n">
-        <v>0.96</v>
+        <v>0.667</v>
       </c>
       <c r="X46" t="n">
-        <v>0.52</v>
+        <v>0.333</v>
       </c>
       <c r="Y46" t="n">
-        <v>3.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>5.72</v>
+        <v>2.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.608</v>
+        <v>0.6</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.52</v>
+        <v>0.667</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.371</v>
+        <v>0.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.12</v>
+        <v>0.167</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.231</v>
+        <v>0.333</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.48</v>
+        <v>0.333</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.8</v>
+        <v>0.333</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AL46" t="n">
-        <v>3.56</v>
+        <v>3.167</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.247</v>
+        <v>0.316</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>24:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>12.326</v>
+        <v>8.606999999999999</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.453</v>
+        <v>0.512</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.494</v>
+        <v>0.538</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.847</v>
+        <v>0.91</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.143</v>
+        <v>0.155</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.199</v>
+        <v>0.122</v>
       </c>
       <c r="AU46" t="n">
-        <v>2.068</v>
+        <v>0.75</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.226</v>
+        <v>0.258</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.107</v>
+        <v>0.155</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.131</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#50 J. HANDS (Per Game)</t>
+          <t>#99 T. NAKIC (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>0.581</v>
       </c>
       <c r="E47" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5</v>
+        <v>1.323</v>
       </c>
       <c r="G47" t="n">
-        <v>3.5</v>
+        <v>3.452</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5</v>
+        <v>1.161</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>1.323</v>
       </c>
       <c r="J47" t="n">
-        <v>1.5</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>1.484</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>0.806</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5</v>
+        <v>0.581</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>0.258</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.5</v>
+        <v>0.419</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.5</v>
+        <v>0.419</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>1.194</v>
       </c>
       <c r="T47" t="n">
-        <v>5</v>
+        <v>208</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.065</v>
       </c>
       <c r="V47" t="n">
-        <v>1</v>
+        <v>0.355</v>
       </c>
       <c r="W47" t="n">
-        <v>1</v>
+        <v>0.484</v>
       </c>
       <c r="X47" t="n">
-        <v>0.5</v>
+        <v>0.226</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.5</v>
+        <v>1.581</v>
       </c>
       <c r="Z47" t="n">
-        <v>3</v>
+        <v>1.871</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.5</v>
+        <v>0.845</v>
       </c>
       <c r="AB47" t="n">
-        <v>1</v>
+        <v>0.097</v>
       </c>
       <c r="AC47" t="n">
-        <v>1</v>
+        <v>0.226</v>
       </c>
       <c r="AD47" t="n">
-        <v>1</v>
+        <v>0.429</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.5</v>
+        <v>0.226</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>0.581</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.5</v>
+        <v>0.742</v>
       </c>
       <c r="AL47" t="n">
-        <v>3.5</v>
+        <v>2.161</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.143</v>
+        <v>0.343</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>8.94</v>
+        <v>5.453</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.393</v>
+        <v>0.576</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.403</v>
+        <v>0.625</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.671</v>
+        <v>1.154</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.168</v>
+        <v>0.077</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.261</v>
       </c>
       <c r="AU47" t="n">
-        <v>1</v>
+        <v>2.231</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.296</v>
+        <v>0.124</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.161</v>
+        <v>0.081</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.052</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#99 T. NAKIC (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>6.481</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.593</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1.037</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>3.407</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.185</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1.481</v>
+        <v>2.094</v>
       </c>
       <c r="L48" t="n">
-        <v>0.778</v>
+        <v>1.406</v>
       </c>
       <c r="M48" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.444</v>
+        <v>0.969</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.778</v>
+        <v>0.25</v>
       </c>
       <c r="S48" t="n">
-        <v>1.259</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.148</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0.259</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.519</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.259</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.412</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.852</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>2.148</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.397</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>5.492</v>
+        <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.596</v>
+        <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.642</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.082</v>
+        <v>0</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>90.53100000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>21.125</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>38.125</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>10.406</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>29.281</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>17.062</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>22.969</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>16.344</v>
       </c>
       <c r="K49" t="n">
-        <v>2.036</v>
+        <v>26.469</v>
       </c>
       <c r="L49" t="n">
-        <v>1.429</v>
+        <v>11.375</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>7.344</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.594</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>12.375</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>11.406</v>
       </c>
       <c r="R49" t="n">
-        <v>0.25</v>
+        <v>23.719</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>21.938</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3223</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>11.312</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>11.219</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>7.188</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>4.156</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>30.781</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>43.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>0.712</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>11.469</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>0.436</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>2.406</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>6.375</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.377</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>3.062</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>7.188</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>0.426</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>7.344</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>22.094</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>0.332</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:33</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>89.887</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.007</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>0.253</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>1.321</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -7991,477 +7991,159 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>84.09399999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>21.594</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>42.594</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>7.562</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>23.062</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>18.219</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>24.594</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>15.344</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>25.531</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>11.219</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>6.062</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.594</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>13.031</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>12.125</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>22.406</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>23.625</v>
       </c>
       <c r="T50" t="n">
-        <v>62</v>
+        <v>2949</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>11.312</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>5.281</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>3.281</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>31.812</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>45.656</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>0.697</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>12.875</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>0.388</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>8.656000000000001</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>0.347</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.688</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>4.562</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>5.875</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>0.318</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:33</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>1</v>
+        <v>89.509</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>0.502</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>0.277</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>1.177</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>0.199</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>28</v>
-      </c>
-      <c r="C51" t="n">
-        <v>90.036</v>
-      </c>
-      <c r="D51" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="E51" t="n">
-        <v>37.821</v>
-      </c>
-      <c r="F51" t="n">
-        <v>10.536</v>
-      </c>
-      <c r="G51" t="n">
-        <v>28.929</v>
-      </c>
-      <c r="H51" t="n">
-        <v>16.929</v>
-      </c>
-      <c r="I51" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="J51" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="K51" t="n">
-        <v>26.107</v>
-      </c>
-      <c r="L51" t="n">
-        <v>11.429</v>
-      </c>
-      <c r="M51" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4.643</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>12.821</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>11.821</v>
-      </c>
-      <c r="R51" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="S51" t="n">
-        <v>21.607</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2806</v>
-      </c>
-      <c r="U51" t="n">
-        <v>11.643</v>
-      </c>
-      <c r="V51" t="n">
-        <v>10.964</v>
-      </c>
-      <c r="W51" t="n">
-        <v>6.857</v>
-      </c>
-      <c r="X51" t="n">
-        <v>3.929</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>30.821</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>43.429</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>4.643</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>10.964</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>2.214</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>6.179</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>3.071</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>7.143</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>7.464</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>21.786</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>200:53</t>
-        </is>
-      </c>
-      <c r="AO51" t="n">
-        <v>89.581</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>1.287</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>28</v>
-      </c>
-      <c r="C52" t="n">
-        <v>83.179</v>
-      </c>
-      <c r="D52" t="n">
-        <v>21.429</v>
-      </c>
-      <c r="E52" t="n">
-        <v>42.571</v>
-      </c>
-      <c r="F52" t="n">
-        <v>7.464</v>
-      </c>
-      <c r="G52" t="n">
-        <v>22.321</v>
-      </c>
-      <c r="H52" t="n">
-        <v>17.929</v>
-      </c>
-      <c r="I52" t="n">
-        <v>24.179</v>
-      </c>
-      <c r="J52" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="K52" t="n">
-        <v>25.036</v>
-      </c>
-      <c r="L52" t="n">
-        <v>10.821</v>
-      </c>
-      <c r="M52" t="n">
-        <v>6.179</v>
-      </c>
-      <c r="N52" t="n">
-        <v>4.571</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>12.286</v>
-      </c>
-      <c r="R52" t="n">
-        <v>22.143</v>
-      </c>
-      <c r="S52" t="n">
-        <v>23.429</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2543</v>
-      </c>
-      <c r="U52" t="n">
-        <v>10.321</v>
-      </c>
-      <c r="V52" t="n">
-        <v>10.571</v>
-      </c>
-      <c r="W52" t="n">
-        <v>5.536</v>
-      </c>
-      <c r="X52" t="n">
-        <v>3.429</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>31.464</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>45.286</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>4.964</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>12.929</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0.384</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>2.929</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>8.536</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.714</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>17.571</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>200:53</t>
-        </is>
-      </c>
-      <c r="AO52" t="n">
-        <v>88.78100000000001</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>0.9370000000000001</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>1.151</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="AY52" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_UCAM Murcia.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_UCAM Murcia.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2512.4</v>
+        <v>2680.84</v>
       </c>
       <c r="C2" t="n">
-        <v>2508.84</v>
+        <v>2675.64</v>
       </c>
       <c r="D2" t="n">
-        <v>115.4716920967459</v>
+        <v>116.3459957243874</v>
       </c>
       <c r="E2" t="n">
-        <v>107.2607260726073</v>
+        <v>107.4883018642269</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5449698655540102</v>
+        <v>0.5507846556233653</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1376720901126408</v>
+        <v>0.1383884275941302</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3082133784928027</v>
+        <v>0.3076305220883534</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2531293463143254</v>
+        <v>0.2554489973844812</v>
       </c>
       <c r="J2" t="n">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="K2" t="n">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="L2" t="n">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="M2" t="n">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="N2" t="n">
-        <v>985</v>
+        <v>1059</v>
       </c>
       <c r="O2" t="n">
-        <v>1384</v>
+        <v>1481</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6416318961520631</v>
+        <v>0.6455972101133391</v>
       </c>
       <c r="Q2" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="R2" t="n">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1701437181270283</v>
+        <v>0.1673931996512642</v>
       </c>
       <c r="T2" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="U2" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="V2" t="n">
-        <v>0.09457579972183588</v>
+        <v>0.09328683522231909</v>
       </c>
       <c r="W2" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="X2" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1066295781177561</v>
+        <v>0.1054925893635571</v>
       </c>
       <c r="Z2" t="n">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="AA2" t="n">
-        <v>707</v>
+        <v>759</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3277700509967548</v>
+        <v>0.3308631211857018</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7117052023121387</v>
+        <v>0.7150573936529372</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4359673024523161</v>
+        <v>0.4296875</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3774509803921569</v>
+        <v>0.3785046728971962</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4260869565217391</v>
+        <v>0.4380165289256198</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3323903818953324</v>
+        <v>0.3386034255599473</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.423410404624277</v>
+        <v>1.430114787305874</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7549019607843137</v>
+        <v>0.7570093457943925</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.066168623265742</v>
+        <v>1.087912087912088</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.86810551558753</v>
+        <v>0.8853932584269663</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9862637362637363</v>
+        <v>0.9921671018276762</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.729323308270677</v>
+        <v>1.697986577181208</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.320707070707071</v>
+        <v>1.327830188679245</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.446969696969697</v>
+        <v>5.410377358490566</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.767676767676767</v>
+        <v>6.738207547169812</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.5125</v>
+        <v>78.84823529411766</v>
       </c>
       <c r="C3" t="n">
-        <v>78.40125</v>
+        <v>78.69529411764707</v>
       </c>
       <c r="D3" t="n">
-        <v>115.4716920967459</v>
+        <v>116.3459957243874</v>
       </c>
       <c r="E3" t="n">
-        <v>107.2607260726073</v>
+        <v>107.4883018642269</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5449698655540102</v>
+        <v>0.5507846556233653</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1376720901126408</v>
+        <v>0.1383884275941303</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3082133784928027</v>
+        <v>0.3076305220883535</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2531293463143254</v>
+        <v>0.2554489973844812</v>
       </c>
       <c r="J3" t="n">
-        <v>11.3125</v>
+        <v>11.58823529411765</v>
       </c>
       <c r="K3" t="n">
-        <v>11.21875</v>
+        <v>11.17647058823529</v>
       </c>
       <c r="L3" t="n">
-        <v>7.1875</v>
+        <v>7.441176470588236</v>
       </c>
       <c r="M3" t="n">
-        <v>11.40625</v>
+        <v>11.52941176470588</v>
       </c>
       <c r="N3" t="n">
-        <v>30.78125</v>
+        <v>31.14705882352941</v>
       </c>
       <c r="O3" t="n">
-        <v>43.25</v>
+        <v>43.55882352941177</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6416318961520631</v>
+        <v>0.6455972101133393</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>4.852941176470588</v>
       </c>
       <c r="R3" t="n">
-        <v>11.46875</v>
+        <v>11.29411764705882</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1701437181270283</v>
+        <v>0.1673931996512642</v>
       </c>
       <c r="T3" t="n">
-        <v>2.40625</v>
+        <v>2.382352941176471</v>
       </c>
       <c r="U3" t="n">
-        <v>6.375</v>
+        <v>6.294117647058823</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09457579972183588</v>
+        <v>0.09328683522231909</v>
       </c>
       <c r="W3" t="n">
-        <v>3.0625</v>
+        <v>3.117647058823529</v>
       </c>
       <c r="X3" t="n">
-        <v>7.1875</v>
+        <v>7.117647058823529</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1066295781177561</v>
+        <v>0.1054925893635571</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.34375</v>
+        <v>7.558823529411764</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.09375</v>
+        <v>22.32352941176471</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3277700509967548</v>
+        <v>0.3308631211857018</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7117052023121387</v>
+        <v>0.7150573936529372</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4359673024523161</v>
+        <v>0.4296874999999999</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3774509803921569</v>
+        <v>0.3785046728971962</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4260869565217391</v>
+        <v>0.4380165289256199</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3323903818953324</v>
+        <v>0.3386034255599473</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.423410404624277</v>
+        <v>1.430114787305874</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7549019607843137</v>
+        <v>0.7570093457943925</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.066168623265742</v>
+        <v>1.087912087912088</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.86810551558753</v>
+        <v>0.8853932584269663</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9862637362637363</v>
+        <v>0.9921671018276761</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.729323308270677</v>
+        <v>1.697986577181208</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.320707070707071</v>
+        <v>1.327830188679245</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.446969696969697</v>
+        <v>5.410377358490566</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.767676767676767</v>
+        <v>6.738207547169812</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2505.28</v>
+        <v>2670.44</v>
       </c>
       <c r="C4" t="n">
-        <v>2508.84</v>
+        <v>2675.64</v>
       </c>
       <c r="D4" t="n">
-        <v>107.2607260726073</v>
+        <v>107.4883018642269</v>
       </c>
       <c r="E4" t="n">
-        <v>115.4716920967459</v>
+        <v>116.3459957243874</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5016658733936221</v>
+        <v>0.5024641577060932</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1455863253592526</v>
+        <v>0.1458327871431193</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2976782752902156</v>
+        <v>0.297191887675507</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2774869109947644</v>
+        <v>0.2836021505376344</v>
       </c>
       <c r="J4" t="n">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="K4" t="n">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="L4" t="n">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="M4" t="n">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="N4" t="n">
-        <v>1018</v>
+        <v>1103</v>
       </c>
       <c r="O4" t="n">
-        <v>1461</v>
+        <v>1585</v>
       </c>
       <c r="P4" t="n">
-        <v>0.695383150880533</v>
+        <v>0.7101254480286738</v>
       </c>
       <c r="Q4" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="R4" t="n">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1960970966206568</v>
+        <v>0.1922043010752688</v>
       </c>
       <c r="T4" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="U4" t="n">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1318419800095193</v>
+        <v>0.1326164874551971</v>
       </c>
       <c r="W4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X4" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06949071870537839</v>
+        <v>0.06810035842293907</v>
       </c>
       <c r="Z4" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="AA4" t="n">
-        <v>592</v>
+        <v>621</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2817705854355069</v>
+        <v>0.2782258064516129</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6967830253251198</v>
+        <v>0.6958990536277603</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3883495145631068</v>
+        <v>0.3869463869463869</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3465703971119133</v>
+        <v>0.347972972972973</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.3618421052631579</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3175675675675675</v>
+        <v>0.322061191626409</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.39356605065024</v>
+        <v>1.391798107255521</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6931407942238267</v>
+        <v>0.6959459459459459</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.983739837398374</v>
+        <v>0.9896507115135834</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.8066037735849056</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.008356545961003</v>
+        <v>1.039370078740157</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.60952380952381</v>
+        <v>1.617391304347826</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.177458033573141</v>
+        <v>1.175280898876405</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.038369304556355</v>
+        <v>5.015730337078652</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.215827338129497</v>
+        <v>6.191011235955056</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.28999999999999</v>
+        <v>78.54235294117646</v>
       </c>
       <c r="C5" t="n">
-        <v>78.40125</v>
+        <v>78.69529411764707</v>
       </c>
       <c r="D5" t="n">
-        <v>107.2607260726073</v>
+        <v>107.4883018642269</v>
       </c>
       <c r="E5" t="n">
-        <v>115.4716920967459</v>
+        <v>116.3459957243874</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5016658733936221</v>
+        <v>0.5024641577060931</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1455863253592526</v>
+        <v>0.1458327871431193</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2976782752902156</v>
+        <v>0.297191887675507</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2774869109947644</v>
+        <v>0.2836021505376344</v>
       </c>
       <c r="J5" t="n">
-        <v>9.75</v>
+        <v>10.05882352941176</v>
       </c>
       <c r="K5" t="n">
-        <v>11.3125</v>
+        <v>11.64705882352941</v>
       </c>
       <c r="L5" t="n">
-        <v>5.28125</v>
+        <v>5.470588235294118</v>
       </c>
       <c r="M5" t="n">
-        <v>12.125</v>
+        <v>12.17647058823529</v>
       </c>
       <c r="N5" t="n">
-        <v>31.8125</v>
+        <v>32.44117647058823</v>
       </c>
       <c r="O5" t="n">
-        <v>45.65625</v>
+        <v>46.61764705882353</v>
       </c>
       <c r="P5" t="n">
-        <v>0.695383150880533</v>
+        <v>0.7101254480286737</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>4.882352941176471</v>
       </c>
       <c r="R5" t="n">
-        <v>12.875</v>
+        <v>12.61764705882353</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1960970966206568</v>
+        <v>0.1922043010752688</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>3.029411764705882</v>
       </c>
       <c r="U5" t="n">
-        <v>8.65625</v>
+        <v>8.705882352941176</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1318419800095193</v>
+        <v>0.1326164874551971</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6875</v>
+        <v>1.617647058823529</v>
       </c>
       <c r="X5" t="n">
-        <v>4.5625</v>
+        <v>4.470588235294118</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06949071870537839</v>
+        <v>0.06810035842293906</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.875</v>
+        <v>5.882352941176471</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.5</v>
+        <v>18.26470588235294</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2817705854355069</v>
+        <v>0.2782258064516129</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6967830253251198</v>
+        <v>0.6958990536277602</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3883495145631068</v>
+        <v>0.386946386946387</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3465703971119133</v>
+        <v>0.347972972972973</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.3618421052631579</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3175675675675675</v>
+        <v>0.322061191626409</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.39356605065024</v>
+        <v>1.39179810725552</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6931407942238267</v>
+        <v>0.6959459459459459</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.983739837398374</v>
+        <v>0.9896507115135835</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.8066037735849056</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.008356545961003</v>
+        <v>1.039370078740157</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.60952380952381</v>
+        <v>1.617391304347826</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.177458033573141</v>
+        <v>1.175280898876405</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.038369304556355</v>
+        <v>5.015730337078653</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.215827338129497</v>
+        <v>6.191011235955057</v>
       </c>
     </row>
     <row r="7">
@@ -1419,16 +1419,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="D8" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E8" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1437,22 +1437,22 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I8" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K8" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N8" t="n">
         <v>11</v>
@@ -1461,49 +1461,49 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Q8" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="R8" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="S8" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="T8" t="n">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="U8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V8" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W8" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y8" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="Z8" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.699</v>
       </c>
       <c r="AB8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AC8" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.554</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
@@ -1534,38 +1534,38 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>527:51</t>
+          <t>562:08</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>303.8</v>
+        <v>319.12</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.675</v>
+        <v>0.679</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.139</v>
+        <v>1.15</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.168</v>
+        <v>0.166</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.38</v>
+        <v>0.373</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.569</v>
+        <v>0.585</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.258</v>
+        <v>0.254</v>
       </c>
       <c r="AW8" t="n">
         <v>0.11</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.201</v>
+        <v>0.207</v>
       </c>
       <c r="AY8" t="n">
         <v>0.033</v>
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E9" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F9" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="H9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I9" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J9" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L9" t="n">
         <v>11</v>
       </c>
       <c r="M9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N9" t="n">
         <v>16</v>
@@ -1620,49 +1620,49 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>66</v>
+      </c>
+      <c r="R9" t="n">
+        <v>66</v>
+      </c>
+      <c r="S9" t="n">
+        <v>76</v>
+      </c>
+      <c r="T9" t="n">
+        <v>289</v>
+      </c>
+      <c r="U9" t="n">
         <v>59</v>
       </c>
-      <c r="Q9" t="n">
-        <v>59</v>
-      </c>
-      <c r="R9" t="n">
-        <v>63</v>
-      </c>
-      <c r="S9" t="n">
-        <v>70</v>
-      </c>
-      <c r="T9" t="n">
-        <v>259</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>49</v>
       </c>
-      <c r="V9" t="n">
-        <v>46</v>
-      </c>
       <c r="W9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="X9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="Z9" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.791</v>
+        <v>0.788</v>
       </c>
       <c r="AB9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.25</v>
+        <v>0.268</v>
       </c>
       <c r="AE9" t="n">
         <v>5</v>
@@ -1674,60 +1674,60 @@
         <v>0.227</v>
       </c>
       <c r="AH9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.389</v>
+        <v>0.421</v>
       </c>
       <c r="AK9" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AL9" t="n">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.338</v>
+        <v>0.335</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>527:22</t>
+          <t>565:56</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>391.16</v>
+        <v>424.04</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.51</v>
+        <v>0.519</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.946</v>
+        <v>0.95</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.151</v>
+        <v>0.156</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.242</v>
+        <v>0.23</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.983</v>
+        <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.333</v>
+        <v>0.335</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.065</v>
+        <v>0.068</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1737,22 +1737,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H10" t="n">
         <v>27</v>
@@ -1764,7 +1764,7 @@
         <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L10" t="n">
         <v>37</v>
@@ -1773,7 +1773,7 @@
         <v>19</v>
       </c>
       <c r="N10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1785,13 +1785,13 @@
         <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="S10" t="n">
         <v>33</v>
       </c>
       <c r="T10" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="U10" t="n">
         <v>19</v>
@@ -1800,19 +1800,19 @@
         <v>30</v>
       </c>
       <c r="W10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="X10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AB10" t="n">
         <v>3</v>
@@ -1842,51 +1842,51 @@
         <v>0.282</v>
       </c>
       <c r="AK10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.261</v>
+        <v>0.292</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>535:43</t>
+          <t>549:24</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>150.72</v>
+        <v>152.72</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.478</v>
+        <v>0.491</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.52</v>
+        <v>0.531</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.902</v>
+        <v>0.923</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.237</v>
+        <v>0.233</v>
       </c>
       <c r="AU10" t="n">
         <v>1.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.126</v>
+        <v>0.124</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.226</v>
+        <v>0.222</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="11">
@@ -2055,67 +2055,67 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>573</v>
+        <v>606</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E12" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="F12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G12" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="H12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I12" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="J12" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="K12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M12" t="n">
         <v>26</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="S12" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="T12" t="n">
-        <v>555</v>
+        <v>587</v>
       </c>
       <c r="U12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="V12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="W12" t="n">
         <v>45</v>
@@ -2124,31 +2124,31 @@
         <v>27</v>
       </c>
       <c r="Y12" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="Z12" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.718</v>
+        <v>0.719</v>
       </c>
       <c r="AB12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.516</v>
+        <v>0.505</v>
       </c>
       <c r="AE12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.406</v>
+        <v>0.403</v>
       </c>
       <c r="AH12" t="n">
         <v>6</v>
@@ -2160,30 +2160,30 @@
         <v>0.4</v>
       </c>
       <c r="AK12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AL12" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>814:27</t>
+          <t>860:15</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>552.48</v>
+        <v>583.4400000000001</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.541</v>
+        <v>0.543</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.579</v>
+        <v>0.58</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.037</v>
+        <v>1.039</v>
       </c>
       <c r="AS12" t="n">
         <v>0.105</v>
@@ -2192,16 +2192,16 @@
         <v>0.212</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.379</v>
+        <v>2.426</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.304</v>
+        <v>0.303</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="AY12" t="n">
         <v>0.171</v>
@@ -2373,82 +2373,82 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="D14" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
+      </c>
+      <c r="H14" t="n">
+        <v>70</v>
+      </c>
+      <c r="I14" t="n">
+        <v>91</v>
+      </c>
+      <c r="J14" t="n">
+        <v>61</v>
+      </c>
+      <c r="K14" t="n">
+        <v>116</v>
+      </c>
+      <c r="L14" t="n">
         <v>19</v>
-      </c>
-      <c r="G14" t="n">
-        <v>50</v>
-      </c>
-      <c r="H14" t="n">
-        <v>63</v>
-      </c>
-      <c r="I14" t="n">
-        <v>82</v>
-      </c>
-      <c r="J14" t="n">
-        <v>55</v>
-      </c>
-      <c r="K14" t="n">
-        <v>111</v>
-      </c>
-      <c r="L14" t="n">
-        <v>17</v>
       </c>
       <c r="M14" t="n">
         <v>35</v>
       </c>
       <c r="N14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R14" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="S14" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="T14" t="n">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="U14" t="n">
         <v>32</v>
       </c>
       <c r="V14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="Z14" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="AB14" t="n">
         <v>4</v>
@@ -2460,69 +2460,69 @@
         <v>0.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="AH14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.375</v>
+        <v>0.423</v>
       </c>
       <c r="AK14" t="n">
         <v>10</v>
       </c>
       <c r="AL14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.385</v>
+        <v>0.345</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>653:00</t>
+          <t>697:20</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>218.08</v>
+        <v>234.04</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.584</v>
+        <v>0.585</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.641</v>
+        <v>0.644</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.082</v>
+        <v>1.09</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.156</v>
+        <v>0.154</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.426</v>
+        <v>0.443</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.618</v>
+        <v>1.694</v>
       </c>
       <c r="AV14" t="n">
         <v>0.15</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.059</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="15">
@@ -2532,40 +2532,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C15" t="n">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="D15" t="n">
+        <v>42</v>
+      </c>
+      <c r="E15" t="n">
+        <v>67</v>
+      </c>
+      <c r="F15" t="n">
+        <v>49</v>
+      </c>
+      <c r="G15" t="n">
+        <v>129</v>
+      </c>
+      <c r="H15" t="n">
+        <v>27</v>
+      </c>
+      <c r="I15" t="n">
         <v>38</v>
       </c>
-      <c r="E15" t="n">
-        <v>61</v>
-      </c>
-      <c r="F15" t="n">
-        <v>45</v>
-      </c>
-      <c r="G15" t="n">
-        <v>119</v>
-      </c>
-      <c r="H15" t="n">
-        <v>26</v>
-      </c>
-      <c r="I15" t="n">
-        <v>36</v>
-      </c>
       <c r="J15" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K15" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M15" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N15" t="n">
         <v>15</v>
@@ -2574,25 +2574,25 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R15" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="S15" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="T15" t="n">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="U15" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="V15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="W15" t="n">
         <v>29</v>
@@ -2601,87 +2601,87 @@
         <v>15</v>
       </c>
       <c r="Y15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Z15" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.775</v>
+        <v>0.779</v>
       </c>
       <c r="AB15" t="n">
         <v>5</v>
       </c>
       <c r="AC15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.385</v>
+        <v>0.357</v>
       </c>
       <c r="AE15" t="n">
         <v>4</v>
       </c>
       <c r="AF15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.308</v>
+        <v>0.286</v>
       </c>
       <c r="AH15" t="n">
         <v>17</v>
       </c>
       <c r="AI15" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AK15" t="n">
         <v>32</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>28</v>
-      </c>
       <c r="AL15" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.322</v>
+        <v>0.333</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>593:09</t>
+          <t>636:11</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>215.84</v>
+        <v>234.72</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.586</v>
+        <v>0.589</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.605</v>
+        <v>0.606</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.098</v>
+        <v>1.099</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.144</v>
+        <v>0.138</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.5</v>
+        <v>2.545</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.163</v>
+        <v>0.165</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="AX15" t="n">
         <v>0.124</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.054</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="16">
@@ -2691,16 +2691,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
@@ -2709,22 +2709,22 @@
         <v>20</v>
       </c>
       <c r="H16" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I16" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N16" t="n">
         <v>12</v>
@@ -2733,40 +2733,40 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R16" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="S16" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="T16" t="n">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="U16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V16" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="W16" t="n">
+        <v>6</v>
+      </c>
+      <c r="X16" t="n">
         <v>4</v>
       </c>
-      <c r="X16" t="n">
-        <v>2</v>
-      </c>
       <c r="Y16" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Z16" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.65</v>
+        <v>0.671</v>
       </c>
       <c r="AB16" t="n">
         <v>3</v>
@@ -2806,41 +2806,41 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>320:51</t>
+          <t>340:04</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>82.64</v>
+        <v>89.72</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.393</v>
+        <v>0.406</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.462</v>
+        <v>0.489</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.835</v>
+        <v>0.881</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.097</v>
+        <v>0.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.344</v>
+        <v>0.422</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.875</v>
+        <v>0.889</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.116</v>
+        <v>0.118</v>
       </c>
       <c r="AW16" t="n">
         <v>0.129</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.137</v>
+        <v>0.148</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="17">
@@ -2850,16 +2850,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E17" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2868,82 +2868,82 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I17" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K17" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L17" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N17" t="n">
+        <v>31</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>26</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>24</v>
-      </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R17" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="S17" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="T17" t="n">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="U17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="V17" t="n">
         <v>40</v>
       </c>
       <c r="W17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="Z17" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="AB17" t="n">
         <v>20</v>
       </c>
       <c r="AC17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.465</v>
+        <v>0.455</v>
       </c>
       <c r="AE17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -2965,29 +2965,29 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>616:29</t>
+          <t>655:00</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>190.6</v>
+        <v>203.68</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.58</v>
+        <v>0.575</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.615</v>
+        <v>0.611</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.076</v>
+        <v>1.065</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.326</v>
+        <v>0.336</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.042</v>
+        <v>1</v>
       </c>
       <c r="AV17" t="n">
         <v>0.139</v>
@@ -2996,10 +2996,10 @@
         <v>0.131</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.16</v>
+        <v>0.157</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="18">
@@ -3009,61 +3009,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
         <v>4</v>
       </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
       <c r="T18" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -3078,10 +3078,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
         <v>1</v>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3124,41 +3124,41 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>36:03</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>5</v>
+        <v>10.88</v>
       </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.8</v>
+        <v>0.735</v>
       </c>
       <c r="AS18" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AU18" t="n">
         <v>0.6</v>
       </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
       <c r="AV18" t="n">
-        <v>0.168</v>
+        <v>0.135</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>0.119</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="19">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C20" t="n">
         <v>42</v>
@@ -3354,7 +3354,7 @@
         <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L20" t="n">
         <v>9</v>
@@ -3375,10 +3375,10 @@
         <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T20" t="n">
         <v>52</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>132:29</t>
+          <t>136:09</t>
         </is>
       </c>
       <c r="AO20" t="n">
@@ -3467,13 +3467,13 @@
         <v>0.75</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.123</v>
+        <v>0.119</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.074</v>
+        <v>0.073</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.129</v>
+        <v>0.133</v>
       </c>
       <c r="AY20" t="n">
         <v>0.003</v>
@@ -3626,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="AW21" t="n">
         <v>0.045</v>
@@ -3645,40 +3645,40 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" t="n">
+        <v>180</v>
+      </c>
+      <c r="D22" t="n">
+        <v>26</v>
+      </c>
+      <c r="E22" t="n">
+        <v>52</v>
+      </c>
+      <c r="F22" t="n">
+        <v>37</v>
+      </c>
+      <c r="G22" t="n">
+        <v>74</v>
+      </c>
+      <c r="H22" t="n">
         <v>17</v>
       </c>
-      <c r="C22" t="n">
-        <v>149</v>
-      </c>
-      <c r="D22" t="n">
-        <v>23</v>
-      </c>
-      <c r="E22" t="n">
-        <v>47</v>
-      </c>
-      <c r="F22" t="n">
-        <v>29</v>
-      </c>
-      <c r="G22" t="n">
-        <v>62</v>
-      </c>
-      <c r="H22" t="n">
-        <v>16</v>
-      </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L22" t="n">
         <v>7</v>
       </c>
       <c r="M22" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N22" t="n">
         <v>4</v>
@@ -3687,22 +3687,22 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R22" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T22" t="n">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="U22" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V22" t="n">
         <v>19</v>
@@ -3714,87 +3714,87 @@
         <v>7</v>
       </c>
       <c r="Y22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Z22" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.75</v>
+        <v>0.771</v>
       </c>
       <c r="AB22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.538</v>
+        <v>0.571</v>
       </c>
       <c r="AE22" t="n">
         <v>8</v>
       </c>
       <c r="AF22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.364</v>
+        <v>0.333</v>
       </c>
       <c r="AH22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AK22" t="n">
         <v>23</v>
       </c>
-      <c r="AJ22" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>19</v>
-      </c>
       <c r="AL22" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.487</v>
+        <v>0.523</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>292:34</t>
+          <t>325:34</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>132.8</v>
+        <v>153.24</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.61</v>
+        <v>0.647</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.632</v>
+        <v>0.665</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.122</v>
+        <v>1.175</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.113</v>
+        <v>0.117</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.147</v>
+        <v>0.135</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.4</v>
+        <v>0.389</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.204</v>
+        <v>0.21</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="23">
@@ -3944,7 +3944,7 @@
         <v>2.068</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.226</v>
+        <v>0.225</v>
       </c>
       <c r="AW23" t="n">
         <v>0.034</v>
@@ -3953,7 +3953,7 @@
         <v>0.105</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.099</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="24">
@@ -3963,61 +3963,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D24" t="n">
         <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H24" t="n">
+        <v>14</v>
+      </c>
+      <c r="I24" t="n">
+        <v>15</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>17</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
         <v>5</v>
       </c>
-      <c r="I24" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>6</v>
-      </c>
-      <c r="K24" t="n">
-        <v>13</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>4</v>
       </c>
-      <c r="N24" t="n">
-        <v>2</v>
-      </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R24" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="U24" t="n">
         <v>2</v>
@@ -4026,28 +4026,28 @@
         <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y24" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="AB24" t="n">
         <v>4</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4059,60 +4059,60 @@
         <v>0.333</v>
       </c>
       <c r="AH24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ24" t="n">
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.316</v>
+        <v>0.333</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>89:38</t>
+          <t>122:20</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>51.64</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.512</v>
+        <v>0.49</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.538</v>
+        <v>0.555</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.91</v>
+        <v>0.948</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.155</v>
+        <v>0.146</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.122</v>
+        <v>0.269</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.258</v>
+        <v>0.251</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.155</v>
+        <v>0.149</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="25">
@@ -4122,22 +4122,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C25" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D25" t="n">
         <v>18</v>
       </c>
       <c r="E25" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F25" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G25" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H25" t="n">
         <v>36</v>
@@ -4146,16 +4146,16 @@
         <v>41</v>
       </c>
       <c r="J25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N25" t="n">
         <v>8</v>
@@ -4164,25 +4164,25 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R25" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="S25" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T25" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="U25" t="n">
         <v>33</v>
       </c>
       <c r="V25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W25" t="n">
         <v>15</v>
@@ -4194,10 +4194,10 @@
         <v>49</v>
       </c>
       <c r="Z25" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.845</v>
+        <v>0.831</v>
       </c>
       <c r="AB25" t="n">
         <v>3</v>
@@ -4227,51 +4227,51 @@
         <v>0.45</v>
       </c>
       <c r="AK25" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL25" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.343</v>
+        <v>0.361</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>608:56</t>
+          <t>640:30</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>169.04</v>
+        <v>176.04</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.576</v>
+        <v>0.583</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.625</v>
+        <v>0.629</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.154</v>
+        <v>1.159</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.261</v>
+        <v>0.25</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.231</v>
+        <v>2.143</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.124</v>
+        <v>0.123</v>
       </c>
       <c r="AW25" t="n">
         <v>0.045</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.081</v>
+        <v>0.082</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="26">
@@ -4281,49 +4281,49 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>34</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>71</v>
+      </c>
+      <c r="L26" t="n">
+        <v>46</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>32</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>67</v>
-      </c>
-      <c r="L26" t="n">
-        <v>45</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>31</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4440,144 +4440,144 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>2897</v>
+        <v>3113</v>
       </c>
       <c r="D27" t="n">
-        <v>676</v>
+        <v>719</v>
       </c>
       <c r="E27" t="n">
-        <v>1220</v>
+        <v>1293</v>
       </c>
       <c r="F27" t="n">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="G27" t="n">
-        <v>937</v>
+        <v>1001</v>
       </c>
       <c r="H27" t="n">
-        <v>546</v>
+        <v>586</v>
       </c>
       <c r="I27" t="n">
-        <v>735</v>
+        <v>786</v>
       </c>
       <c r="J27" t="n">
-        <v>523</v>
+        <v>563</v>
       </c>
       <c r="K27" t="n">
-        <v>847</v>
+        <v>901</v>
       </c>
       <c r="L27" t="n">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="M27" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="N27" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="Q27" t="n">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="R27" t="n">
+        <v>809</v>
+      </c>
+      <c r="S27" t="n">
+        <v>752</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3474</v>
+      </c>
+      <c r="U27" t="n">
+        <v>394</v>
+      </c>
+      <c r="V27" t="n">
+        <v>380</v>
+      </c>
+      <c r="W27" t="n">
+        <v>253</v>
+      </c>
+      <c r="X27" t="n">
+        <v>149</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1059</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>165</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>384</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>81</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>214</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>106</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>242</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>257</v>
+      </c>
+      <c r="AL27" t="n">
         <v>759</v>
       </c>
-      <c r="S27" t="n">
-        <v>702</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3223</v>
-      </c>
-      <c r="U27" t="n">
-        <v>362</v>
-      </c>
-      <c r="V27" t="n">
-        <v>359</v>
-      </c>
-      <c r="W27" t="n">
-        <v>230</v>
-      </c>
-      <c r="X27" t="n">
-        <v>133</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>985</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1384</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.712</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>160</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>367</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.436</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>77</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>204</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>98</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>230</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0.426</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>235</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>707</v>
-      </c>
       <c r="AM27" t="n">
-        <v>0.332</v>
+        <v>0.339</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>6450:00</t>
+          <t>6850:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2876.4</v>
+        <v>3063.84</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.545</v>
+        <v>0.551</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.584</v>
+        <v>0.59</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.007</v>
+        <v>1.016</v>
       </c>
       <c r="AS27" t="n">
         <v>0.138</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.253</v>
+        <v>0.255</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.321</v>
+        <v>1.328</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
@@ -4586,7 +4586,7 @@
         <v>0.062</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4599,150 +4599,150 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>2691</v>
+        <v>2876</v>
       </c>
       <c r="D28" t="n">
-        <v>691</v>
+        <v>739</v>
       </c>
       <c r="E28" t="n">
-        <v>1363</v>
+        <v>1459</v>
       </c>
       <c r="F28" t="n">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="G28" t="n">
-        <v>738</v>
+        <v>773</v>
       </c>
       <c r="H28" t="n">
-        <v>583</v>
+        <v>633</v>
       </c>
       <c r="I28" t="n">
-        <v>787</v>
+        <v>851</v>
       </c>
       <c r="J28" t="n">
-        <v>491</v>
+        <v>523</v>
       </c>
       <c r="K28" t="n">
-        <v>817</v>
+        <v>862</v>
       </c>
       <c r="L28" t="n">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="M28" t="n">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="N28" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="Q28" t="n">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="R28" t="n">
-        <v>717</v>
+        <v>769</v>
       </c>
       <c r="S28" t="n">
-        <v>756</v>
+        <v>807</v>
       </c>
       <c r="T28" t="n">
-        <v>2949</v>
+        <v>3144</v>
       </c>
       <c r="U28" t="n">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="V28" t="n">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="W28" t="n">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="X28" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="Y28" t="n">
-        <v>1018</v>
+        <v>1103</v>
       </c>
       <c r="Z28" t="n">
-        <v>1461</v>
+        <v>1585</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.697</v>
+        <v>0.696</v>
       </c>
       <c r="AB28" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AC28" t="n">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.388</v>
+        <v>0.387</v>
       </c>
       <c r="AE28" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="AF28" t="n">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="AH28" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AI28" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.37</v>
+        <v>0.362</v>
       </c>
       <c r="AK28" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="AL28" t="n">
-        <v>592</v>
+        <v>621</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.318</v>
+        <v>0.322</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>6450:00</t>
+          <t>6850:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>2864.28</v>
+        <v>3051.44</v>
       </c>
       <c r="AP28" t="n">
         <v>0.502</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.55</v>
+        <v>0.552</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="AS28" t="n">
         <v>0.146</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.277</v>
+        <v>0.284</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.177</v>
+        <v>1.175</v>
       </c>
       <c r="AV28" t="n">
         <v>0.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="AX28" t="n">
         <v>0.138</v>
@@ -4815,16 +4815,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>11.533</v>
+        <v>11.469</v>
       </c>
       <c r="D30" t="n">
         <v>4.5</v>
       </c>
       <c r="E30" t="n">
-        <v>6.667</v>
+        <v>6.625</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -4833,79 +4833,79 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.533</v>
+        <v>2.469</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>3.844</v>
       </c>
       <c r="J30" t="n">
-        <v>0.967</v>
+        <v>0.969</v>
       </c>
       <c r="K30" t="n">
-        <v>3.3</v>
+        <v>3.406</v>
       </c>
       <c r="L30" t="n">
-        <v>1.767</v>
+        <v>1.75</v>
       </c>
       <c r="M30" t="n">
-        <v>0.767</v>
+        <v>0.75</v>
       </c>
       <c r="N30" t="n">
-        <v>0.367</v>
+        <v>0.344</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.7</v>
+        <v>1.656</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.7</v>
+        <v>1.656</v>
       </c>
       <c r="R30" t="n">
-        <v>3.767</v>
+        <v>3.75</v>
       </c>
       <c r="S30" t="n">
-        <v>3.9</v>
+        <v>3.812</v>
       </c>
       <c r="T30" t="n">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="U30" t="n">
-        <v>1.533</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
-        <v>1.867</v>
+        <v>1.812</v>
       </c>
       <c r="W30" t="n">
-        <v>0.633</v>
+        <v>0.719</v>
       </c>
       <c r="X30" t="n">
-        <v>0.433</v>
+        <v>0.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.633</v>
+        <v>5.594</v>
       </c>
       <c r="Z30" t="n">
-        <v>8.132999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.699</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.2</v>
+        <v>1.188</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.167</v>
+        <v>2.125</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.554</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.367</v>
+        <v>0.344</v>
       </c>
       <c r="AG30" t="n">
         <v>0.545</v>
@@ -4930,41 +4930,41 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>10.127</v>
+        <v>9.972</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.675</v>
+        <v>0.679</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.139</v>
+        <v>1.15</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.168</v>
+        <v>0.166</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.38</v>
+        <v>0.373</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.569</v>
+        <v>0.585</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.258</v>
+        <v>0.254</v>
       </c>
       <c r="AW30" t="n">
         <v>0.11</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.201</v>
+        <v>0.207</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="31">
@@ -4974,156 +4974,156 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>11.562</v>
+        <v>11.853</v>
       </c>
       <c r="D31" t="n">
-        <v>1.906</v>
+        <v>2.029</v>
       </c>
       <c r="E31" t="n">
-        <v>3.781</v>
+        <v>3.882</v>
       </c>
       <c r="F31" t="n">
-        <v>1.844</v>
+        <v>1.882</v>
       </c>
       <c r="G31" t="n">
-        <v>5.375</v>
+        <v>5.471</v>
       </c>
       <c r="H31" t="n">
-        <v>2.219</v>
+        <v>2.147</v>
       </c>
       <c r="I31" t="n">
-        <v>2.781</v>
+        <v>2.676</v>
       </c>
       <c r="J31" t="n">
-        <v>1.812</v>
+        <v>1.941</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>1.059</v>
       </c>
       <c r="L31" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="M31" t="n">
-        <v>0.469</v>
+        <v>0.471</v>
       </c>
       <c r="N31" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.844</v>
+        <v>1.941</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.844</v>
+        <v>1.941</v>
       </c>
       <c r="R31" t="n">
-        <v>1.969</v>
+        <v>1.941</v>
       </c>
       <c r="S31" t="n">
-        <v>2.188</v>
+        <v>2.235</v>
       </c>
       <c r="T31" t="n">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="U31" t="n">
-        <v>1.531</v>
+        <v>1.735</v>
       </c>
       <c r="V31" t="n">
-        <v>1.438</v>
+        <v>1.441</v>
       </c>
       <c r="W31" t="n">
-        <v>0.844</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="X31" t="n">
-        <v>0.469</v>
+        <v>0.529</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.656</v>
+        <v>3.706</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.625</v>
+        <v>4.706</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.791</v>
+        <v>0.788</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.25</v>
+        <v>1.206</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.25</v>
+        <v>0.268</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.647</v>
       </c>
       <c r="AG31" t="n">
         <v>0.227</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.219</v>
+        <v>0.235</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.389</v>
+        <v>0.421</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.625</v>
+        <v>1.647</v>
       </c>
       <c r="AL31" t="n">
-        <v>4.812</v>
+        <v>4.912</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.338</v>
+        <v>0.335</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>12.224</v>
+        <v>12.472</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.51</v>
+        <v>0.519</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.946</v>
+        <v>0.95</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.151</v>
+        <v>0.156</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.242</v>
+        <v>0.23</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.983</v>
+        <v>1</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.333</v>
+        <v>0.335</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.065</v>
+        <v>0.068</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -5133,88 +5133,88 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C32" t="n">
-        <v>5.037</v>
+        <v>5.036</v>
       </c>
       <c r="D32" t="n">
-        <v>1.074</v>
+        <v>1.071</v>
       </c>
       <c r="E32" t="n">
-        <v>1.926</v>
+        <v>1.893</v>
       </c>
       <c r="F32" t="n">
-        <v>0.63</v>
+        <v>0.643</v>
       </c>
       <c r="G32" t="n">
-        <v>2.296</v>
+        <v>2.25</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0.964</v>
       </c>
       <c r="I32" t="n">
-        <v>1.407</v>
+        <v>1.357</v>
       </c>
       <c r="J32" t="n">
-        <v>0.963</v>
+        <v>0.929</v>
       </c>
       <c r="K32" t="n">
-        <v>4.185</v>
+        <v>4.071</v>
       </c>
       <c r="L32" t="n">
-        <v>1.37</v>
+        <v>1.321</v>
       </c>
       <c r="M32" t="n">
-        <v>0.704</v>
+        <v>0.679</v>
       </c>
       <c r="N32" t="n">
-        <v>0.519</v>
+        <v>0.571</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.741</v>
+        <v>0.714</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.741</v>
+        <v>0.714</v>
       </c>
       <c r="R32" t="n">
-        <v>3.407</v>
+        <v>3.393</v>
       </c>
       <c r="S32" t="n">
-        <v>1.222</v>
+        <v>1.179</v>
       </c>
       <c r="T32" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="U32" t="n">
-        <v>0.704</v>
+        <v>0.679</v>
       </c>
       <c r="V32" t="n">
-        <v>1.111</v>
+        <v>1.071</v>
       </c>
       <c r="W32" t="n">
-        <v>0.37</v>
+        <v>0.464</v>
       </c>
       <c r="X32" t="n">
-        <v>0.259</v>
+        <v>0.286</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.963</v>
+        <v>1.929</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.852</v>
+        <v>2.786</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.111</v>
+        <v>0.107</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.333</v>
+        <v>0.321</v>
       </c>
       <c r="AD32" t="n">
         <v>0.333</v>
@@ -5223,66 +5223,66 @@
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.148</v>
+        <v>0.143</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.407</v>
+        <v>0.393</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.444</v>
+        <v>1.393</v>
       </c>
       <c r="AJ32" t="n">
         <v>0.282</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.222</v>
+        <v>0.25</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.852</v>
+        <v>0.857</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.261</v>
+        <v>0.292</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>5.582</v>
+        <v>5.454</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.478</v>
+        <v>0.491</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.52</v>
+        <v>0.531</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.902</v>
+        <v>0.923</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.237</v>
+        <v>0.233</v>
       </c>
       <c r="AU32" t="n">
         <v>1.3</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.126</v>
+        <v>0.124</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.226</v>
+        <v>0.222</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="33">
@@ -5451,135 +5451,135 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C34" t="n">
-        <v>17.906</v>
+        <v>17.824</v>
       </c>
       <c r="D34" t="n">
-        <v>4.156</v>
+        <v>4.147</v>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>7.912</v>
       </c>
       <c r="F34" t="n">
-        <v>2.219</v>
+        <v>2.206</v>
       </c>
       <c r="G34" t="n">
-        <v>5.844</v>
+        <v>5.824</v>
       </c>
       <c r="H34" t="n">
-        <v>2.938</v>
+        <v>2.912</v>
       </c>
       <c r="I34" t="n">
-        <v>3.656</v>
+        <v>3.706</v>
       </c>
       <c r="J34" t="n">
-        <v>4.312</v>
+        <v>4.353</v>
       </c>
       <c r="K34" t="n">
-        <v>1.406</v>
+        <v>1.353</v>
       </c>
       <c r="L34" t="n">
-        <v>0.344</v>
+        <v>0.382</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="N34" t="n">
-        <v>0.281</v>
+        <v>0.294</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.812</v>
+        <v>1.794</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.812</v>
+        <v>1.794</v>
       </c>
       <c r="R34" t="n">
-        <v>1.438</v>
+        <v>1.441</v>
       </c>
       <c r="S34" t="n">
-        <v>3.719</v>
+        <v>3.706</v>
       </c>
       <c r="T34" t="n">
-        <v>555</v>
+        <v>587</v>
       </c>
       <c r="U34" t="n">
-        <v>1.938</v>
+        <v>2.059</v>
       </c>
       <c r="V34" t="n">
-        <v>1.688</v>
+        <v>1.765</v>
       </c>
       <c r="W34" t="n">
-        <v>1.406</v>
+        <v>1.324</v>
       </c>
       <c r="X34" t="n">
-        <v>0.844</v>
+        <v>0.794</v>
       </c>
       <c r="Y34" t="n">
-        <v>4.688</v>
+        <v>4.735</v>
       </c>
       <c r="Z34" t="n">
-        <v>6.531</v>
+        <v>6.588</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.718</v>
+        <v>0.719</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.531</v>
+        <v>1.471</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.969</v>
+        <v>2.912</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.516</v>
+        <v>0.505</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.875</v>
+        <v>0.853</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.156</v>
+        <v>2.118</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.406</v>
+        <v>0.403</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="AJ34" t="n">
         <v>0.4</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.031</v>
+        <v>2.029</v>
       </c>
       <c r="AL34" t="n">
-        <v>5.375</v>
+        <v>5.382</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>25:27</t>
+          <t>25:18</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>17.265</v>
+        <v>17.16</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.541</v>
+        <v>0.543</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.579</v>
+        <v>0.58</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.037</v>
+        <v>1.039</v>
       </c>
       <c r="AS34" t="n">
         <v>0.105</v>
@@ -5588,16 +5588,16 @@
         <v>0.212</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.379</v>
+        <v>2.426</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.304</v>
+        <v>0.303</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="AY34" t="n">
         <v>0.171</v>
@@ -5769,156 +5769,156 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>7.375</v>
+        <v>7.5</v>
       </c>
       <c r="D36" t="n">
-        <v>1.812</v>
+        <v>1.794</v>
       </c>
       <c r="E36" t="n">
-        <v>3.062</v>
+        <v>3.029</v>
       </c>
       <c r="F36" t="n">
-        <v>0.594</v>
+        <v>0.618</v>
       </c>
       <c r="G36" t="n">
-        <v>1.562</v>
+        <v>1.618</v>
       </c>
       <c r="H36" t="n">
-        <v>1.969</v>
+        <v>2.059</v>
       </c>
       <c r="I36" t="n">
-        <v>2.562</v>
+        <v>2.676</v>
       </c>
       <c r="J36" t="n">
-        <v>1.719</v>
+        <v>1.794</v>
       </c>
       <c r="K36" t="n">
-        <v>3.469</v>
+        <v>3.412</v>
       </c>
       <c r="L36" t="n">
-        <v>0.531</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>1.094</v>
+        <v>1.029</v>
       </c>
       <c r="N36" t="n">
-        <v>0.219</v>
+        <v>0.235</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.062</v>
+        <v>1.059</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.062</v>
+        <v>1.059</v>
       </c>
       <c r="R36" t="n">
-        <v>1.531</v>
+        <v>1.618</v>
       </c>
       <c r="S36" t="n">
-        <v>2.219</v>
+        <v>2.265</v>
       </c>
       <c r="T36" t="n">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="V36" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.676</v>
       </c>
       <c r="W36" t="n">
-        <v>0.969</v>
+        <v>0.971</v>
       </c>
       <c r="X36" t="n">
-        <v>0.594</v>
+        <v>0.588</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.375</v>
+        <v>3.441</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.625</v>
+        <v>4.706</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.625</v>
+        <v>0.588</v>
       </c>
       <c r="AD36" t="n">
         <v>0.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.281</v>
+        <v>0.294</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.375</v>
+        <v>0.412</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.281</v>
+        <v>0.324</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.75</v>
+        <v>0.765</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.375</v>
+        <v>0.423</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.853</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.385</v>
+        <v>0.345</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>6.815</v>
+        <v>6.884</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.584</v>
+        <v>0.585</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.641</v>
+        <v>0.644</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.082</v>
+        <v>1.09</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.156</v>
+        <v>0.154</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.426</v>
+        <v>0.443</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.618</v>
+        <v>1.694</v>
       </c>
       <c r="AV36" t="n">
         <v>0.15</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.059</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="37">
@@ -5928,156 +5928,156 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C37" t="n">
-        <v>8.172000000000001</v>
+        <v>8.323</v>
       </c>
       <c r="D37" t="n">
-        <v>1.31</v>
+        <v>1.355</v>
       </c>
       <c r="E37" t="n">
-        <v>2.103</v>
+        <v>2.161</v>
       </c>
       <c r="F37" t="n">
-        <v>1.552</v>
+        <v>1.581</v>
       </c>
       <c r="G37" t="n">
-        <v>4.103</v>
+        <v>4.161</v>
       </c>
       <c r="H37" t="n">
-        <v>0.897</v>
+        <v>0.871</v>
       </c>
       <c r="I37" t="n">
-        <v>1.241</v>
+        <v>1.226</v>
       </c>
       <c r="J37" t="n">
-        <v>1.724</v>
+        <v>1.806</v>
       </c>
       <c r="K37" t="n">
-        <v>2.379</v>
+        <v>2.387</v>
       </c>
       <c r="L37" t="n">
-        <v>0.448</v>
+        <v>0.516</v>
       </c>
       <c r="M37" t="n">
-        <v>0.966</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>0.517</v>
+        <v>0.484</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="R37" t="n">
-        <v>2.31</v>
+        <v>2.355</v>
       </c>
       <c r="S37" t="n">
-        <v>1.621</v>
+        <v>1.645</v>
       </c>
       <c r="T37" t="n">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="U37" t="n">
-        <v>1.138</v>
+        <v>1.161</v>
       </c>
       <c r="V37" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="X37" t="n">
-        <v>0.517</v>
+        <v>0.484</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.897</v>
+        <v>1.935</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.448</v>
+        <v>2.484</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.775</v>
+        <v>0.779</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.172</v>
+        <v>0.161</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.448</v>
+        <v>0.452</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.385</v>
+        <v>0.357</v>
       </c>
       <c r="AE37" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>3.097</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AO37" t="n">
+        <v>7.572</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AT37" t="n">
         <v>0.138</v>
       </c>
-      <c r="AF37" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.103</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0.966</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>20:27</t>
-        </is>
-      </c>
-      <c r="AO37" t="n">
-        <v>7.443</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.098</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0.144</v>
-      </c>
       <c r="AU37" t="n">
-        <v>2.5</v>
+        <v>2.545</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.163</v>
+        <v>0.165</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="AX37" t="n">
         <v>0.124</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.06</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="38">
@@ -6087,88 +6087,88 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C38" t="n">
-        <v>2.3</v>
+        <v>2.548</v>
       </c>
       <c r="D38" t="n">
-        <v>0.7</v>
+        <v>0.742</v>
       </c>
       <c r="E38" t="n">
-        <v>1.367</v>
+        <v>1.419</v>
       </c>
       <c r="F38" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="G38" t="n">
-        <v>0.667</v>
+        <v>0.645</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7</v>
+        <v>0.871</v>
       </c>
       <c r="I38" t="n">
-        <v>1.033</v>
+        <v>1.226</v>
       </c>
       <c r="J38" t="n">
-        <v>0.233</v>
+        <v>0.258</v>
       </c>
       <c r="K38" t="n">
-        <v>1.367</v>
+        <v>1.516</v>
       </c>
       <c r="L38" t="n">
-        <v>1.267</v>
+        <v>1.29</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3</v>
+        <v>0.323</v>
       </c>
       <c r="N38" t="n">
-        <v>0.4</v>
+        <v>0.387</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.267</v>
+        <v>0.29</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.267</v>
+        <v>0.29</v>
       </c>
       <c r="R38" t="n">
-        <v>1.933</v>
+        <v>1.968</v>
       </c>
       <c r="S38" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.065</v>
       </c>
       <c r="T38" t="n">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="U38" t="n">
-        <v>0.167</v>
+        <v>0.226</v>
       </c>
       <c r="V38" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="W38" t="n">
-        <v>0.133</v>
+        <v>0.194</v>
       </c>
       <c r="X38" t="n">
-        <v>0.067</v>
+        <v>0.129</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.3</v>
+        <v>1.516</v>
       </c>
       <c r="Z38" t="n">
-        <v>2</v>
+        <v>2.258</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.65</v>
+        <v>0.671</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.1</v>
+        <v>0.097</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="AD38" t="n">
         <v>0.273</v>
@@ -6177,16 +6177,16 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.267</v>
+        <v>0.258</v>
       </c>
       <c r="AJ38" t="n">
         <v>0.25</v>
@@ -6195,45 +6195,45 @@
         <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.4</v>
+        <v>0.387</v>
       </c>
       <c r="AM38" t="n">
         <v>0</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>2.755</v>
+        <v>2.894</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.393</v>
+        <v>0.406</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.462</v>
+        <v>0.489</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.835</v>
+        <v>0.881</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.097</v>
+        <v>0.1</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.344</v>
+        <v>0.422</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.875</v>
+        <v>0.889</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.116</v>
+        <v>0.118</v>
       </c>
       <c r="AW38" t="n">
         <v>0.129</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.137</v>
+        <v>0.148</v>
       </c>
       <c r="AY38" t="n">
         <v>0.008</v>
@@ -6246,16 +6246,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C39" t="n">
-        <v>6.406</v>
+        <v>6.382</v>
       </c>
       <c r="D39" t="n">
-        <v>2.5</v>
+        <v>2.471</v>
       </c>
       <c r="E39" t="n">
-        <v>4.312</v>
+        <v>4.294</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -6264,82 +6264,82 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.406</v>
+        <v>1.441</v>
       </c>
       <c r="I39" t="n">
-        <v>2.031</v>
+        <v>2.118</v>
       </c>
       <c r="J39" t="n">
-        <v>0.781</v>
+        <v>0.765</v>
       </c>
       <c r="K39" t="n">
-        <v>2.875</v>
+        <v>2.824</v>
       </c>
       <c r="L39" t="n">
-        <v>2.312</v>
+        <v>2.294</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.912</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.75</v>
+        <v>0.765</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.75</v>
+        <v>0.765</v>
       </c>
       <c r="R39" t="n">
-        <v>2.188</v>
+        <v>2.265</v>
       </c>
       <c r="S39" t="n">
-        <v>2.219</v>
+        <v>2.206</v>
       </c>
       <c r="T39" t="n">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="U39" t="n">
-        <v>0.625</v>
+        <v>0.647</v>
       </c>
       <c r="V39" t="n">
-        <v>1.25</v>
+        <v>1.176</v>
       </c>
       <c r="W39" t="n">
-        <v>0.25</v>
+        <v>0.294</v>
       </c>
       <c r="X39" t="n">
-        <v>0.156</v>
+        <v>0.176</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.969</v>
+        <v>2.971</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.312</v>
+        <v>4.412</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.625</v>
+        <v>0.588</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.344</v>
+        <v>1.294</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.465</v>
+        <v>0.455</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.312</v>
+        <v>0.353</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.706</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>
@@ -6365,25 +6365,25 @@
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>5.956</v>
+        <v>5.991</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.58</v>
+        <v>0.575</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.615</v>
+        <v>0.611</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.076</v>
+        <v>1.065</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.326</v>
+        <v>0.336</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.042</v>
+        <v>1</v>
       </c>
       <c r="AV39" t="n">
         <v>0.139</v>
@@ -6392,10 +6392,10 @@
         <v>0.131</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.16</v>
+        <v>0.157</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="40">
@@ -6405,16 +6405,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C40" t="n">
-        <v>0.308</v>
+        <v>0.533</v>
       </c>
       <c r="D40" t="n">
-        <v>0.154</v>
+        <v>0.2</v>
       </c>
       <c r="E40" t="n">
-        <v>0.154</v>
+        <v>0.333</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -6423,43 +6423,43 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.231</v>
+        <v>0.333</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.231</v>
+        <v>0.333</v>
       </c>
       <c r="R40" t="n">
-        <v>0.308</v>
+        <v>0.467</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T40" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -6474,10 +6474,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.154</v>
+        <v>0.333</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.154</v>
+        <v>0.333</v>
       </c>
       <c r="AA40" t="n">
         <v>1</v>
@@ -6486,7 +6486,7 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -6520,41 +6520,41 @@
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>01:01</t>
+          <t>02:24</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>0.385</v>
+        <v>0.725</v>
       </c>
       <c r="AP40" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.8</v>
+        <v>0.735</v>
       </c>
       <c r="AS40" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AU40" t="n">
         <v>0.6</v>
       </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
       <c r="AV40" t="n">
-        <v>0.168</v>
+        <v>0.135</v>
       </c>
       <c r="AW40" t="n">
         <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>0.119</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="41">
@@ -6723,16 +6723,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C42" t="n">
-        <v>1.615</v>
+        <v>1.5</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5</v>
+        <v>0.464</v>
       </c>
       <c r="E42" t="n">
-        <v>0.885</v>
+        <v>0.821</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -6741,49 +6741,49 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.615</v>
+        <v>0.571</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="J42" t="n">
-        <v>0.115</v>
+        <v>0.107</v>
       </c>
       <c r="K42" t="n">
-        <v>0.615</v>
+        <v>0.607</v>
       </c>
       <c r="L42" t="n">
-        <v>0.346</v>
+        <v>0.321</v>
       </c>
       <c r="M42" t="n">
-        <v>0.154</v>
+        <v>0.143</v>
       </c>
       <c r="N42" t="n">
-        <v>0.192</v>
+        <v>0.179</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.154</v>
+        <v>0.143</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.154</v>
+        <v>0.143</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="T42" t="n">
         <v>52</v>
       </c>
       <c r="U42" t="n">
-        <v>0.077</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="V42" t="n">
-        <v>0.462</v>
+        <v>0.429</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -6792,28 +6792,28 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.962</v>
+        <v>0.893</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.231</v>
+        <v>1.143</v>
       </c>
       <c r="AA42" t="n">
         <v>0.781</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.115</v>
+        <v>0.107</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.269</v>
+        <v>0.25</v>
       </c>
       <c r="AD42" t="n">
         <v>0.429</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.192</v>
+        <v>0.179</v>
       </c>
       <c r="AG42" t="n">
         <v>0.2</v>
@@ -6838,11 +6838,11 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>1.394</v>
+        <v>1.294</v>
       </c>
       <c r="AP42" t="n">
         <v>0.5649999999999999</v>
@@ -6863,16 +6863,16 @@
         <v>0.75</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.123</v>
+        <v>0.119</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.074</v>
+        <v>0.073</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.129</v>
+        <v>0.133</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="43">
@@ -7022,7 +7022,7 @@
         <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="AW43" t="n">
         <v>0.045</v>
@@ -7041,156 +7041,156 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C44" t="n">
-        <v>8.765000000000001</v>
+        <v>9.474</v>
       </c>
       <c r="D44" t="n">
-        <v>1.353</v>
+        <v>1.368</v>
       </c>
       <c r="E44" t="n">
-        <v>2.765</v>
+        <v>2.737</v>
       </c>
       <c r="F44" t="n">
-        <v>1.706</v>
+        <v>1.947</v>
       </c>
       <c r="G44" t="n">
-        <v>3.647</v>
+        <v>3.895</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.895</v>
       </c>
       <c r="I44" t="n">
-        <v>1.176</v>
+        <v>1.105</v>
       </c>
       <c r="J44" t="n">
-        <v>0.353</v>
+        <v>0.368</v>
       </c>
       <c r="K44" t="n">
-        <v>1.765</v>
+        <v>1.684</v>
       </c>
       <c r="L44" t="n">
-        <v>0.412</v>
+        <v>0.368</v>
       </c>
       <c r="M44" t="n">
-        <v>0.471</v>
+        <v>0.579</v>
       </c>
       <c r="N44" t="n">
-        <v>0.235</v>
+        <v>0.211</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.882</v>
+        <v>0.947</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.882</v>
+        <v>0.947</v>
       </c>
       <c r="R44" t="n">
-        <v>1.824</v>
+        <v>1.684</v>
       </c>
       <c r="S44" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.947</v>
       </c>
       <c r="T44" t="n">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="U44" t="n">
-        <v>0.765</v>
+        <v>0.947</v>
       </c>
       <c r="V44" t="n">
-        <v>1.118</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.421</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.842</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1.579</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>2.316</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AO44" t="n">
+        <v>8.065</v>
+      </c>
+      <c r="AP44" t="n">
         <v>0.647</v>
       </c>
-      <c r="X44" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.412</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.882</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.294</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1.353</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1.118</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>2.294</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AO44" t="n">
-        <v>7.812</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0.61</v>
-      </c>
       <c r="AQ44" t="n">
-        <v>0.632</v>
+        <v>0.665</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.122</v>
+        <v>1.175</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.113</v>
+        <v>0.117</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.147</v>
+        <v>0.135</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.4</v>
+        <v>0.389</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.204</v>
+        <v>0.21</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="45">
@@ -7340,7 +7340,7 @@
         <v>2.068</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.226</v>
+        <v>0.225</v>
       </c>
       <c r="AW45" t="n">
         <v>0.034</v>
@@ -7349,7 +7349,7 @@
         <v>0.105</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="46">
@@ -7359,106 +7359,106 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C46" t="n">
-        <v>7.833</v>
+        <v>8.125</v>
       </c>
       <c r="D46" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T46" t="n">
+        <v>56</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC46" t="n">
         <v>1.5</v>
       </c>
-      <c r="E46" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N46" t="n">
+      <c r="AD46" t="n">
         <v>0.333</v>
       </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="T46" t="n">
-        <v>36</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AE46" t="n">
-        <v>0.167</v>
+        <v>0.125</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="AG46" t="n">
         <v>0.333</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AJ46" t="n">
         <v>1</v>
@@ -7467,48 +7467,48 @@
         <v>1</v>
       </c>
       <c r="AL46" t="n">
-        <v>3.167</v>
+        <v>3</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.316</v>
+        <v>0.333</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>8.606999999999999</v>
+        <v>8.574999999999999</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.512</v>
+        <v>0.49</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.538</v>
+        <v>0.555</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.91</v>
+        <v>0.948</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.155</v>
+        <v>0.146</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.122</v>
+        <v>0.269</v>
       </c>
       <c r="AU46" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.258</v>
+        <v>0.251</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.155</v>
+        <v>0.149</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="47">
@@ -7518,156 +7518,156 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C47" t="n">
-        <v>6.29</v>
+        <v>6.182</v>
       </c>
       <c r="D47" t="n">
-        <v>0.581</v>
+        <v>0.545</v>
       </c>
       <c r="E47" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3.394</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1.485</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.697</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="T47" t="n">
+        <v>217</v>
+      </c>
+      <c r="U47" t="n">
         <v>1</v>
       </c>
-      <c r="F47" t="n">
-        <v>1.323</v>
-      </c>
-      <c r="G47" t="n">
-        <v>3.452</v>
-      </c>
-      <c r="H47" t="n">
-        <v>1.161</v>
-      </c>
-      <c r="I47" t="n">
-        <v>1.323</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1.484</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="S47" t="n">
-        <v>1.194</v>
-      </c>
-      <c r="T47" t="n">
-        <v>208</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.065</v>
-      </c>
       <c r="V47" t="n">
-        <v>0.355</v>
+        <v>0.424</v>
       </c>
       <c r="W47" t="n">
-        <v>0.484</v>
+        <v>0.455</v>
       </c>
       <c r="X47" t="n">
-        <v>0.226</v>
+        <v>0.212</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.581</v>
+        <v>1.485</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.871</v>
+        <v>1.788</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.845</v>
+        <v>0.831</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.097</v>
+        <v>0.091</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.226</v>
+        <v>0.212</v>
       </c>
       <c r="AD47" t="n">
         <v>0.429</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.226</v>
+        <v>0.212</v>
       </c>
       <c r="AG47" t="n">
         <v>0.286</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.581</v>
+        <v>0.545</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.29</v>
+        <v>1.212</v>
       </c>
       <c r="AJ47" t="n">
         <v>0.45</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.742</v>
+        <v>0.788</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.161</v>
+        <v>2.182</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.343</v>
+        <v>0.361</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>5.453</v>
+        <v>5.335</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.576</v>
+        <v>0.583</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.625</v>
+        <v>0.629</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.154</v>
+        <v>1.159</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.261</v>
+        <v>0.25</v>
       </c>
       <c r="AU47" t="n">
-        <v>2.231</v>
+        <v>2.143</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.124</v>
+        <v>0.123</v>
       </c>
       <c r="AW47" t="n">
         <v>0.045</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.081</v>
+        <v>0.082</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="48">
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -7704,10 +7704,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>2.094</v>
+        <v>2.088</v>
       </c>
       <c r="L48" t="n">
-        <v>1.406</v>
+        <v>1.353</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -7719,13 +7719,13 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.969</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -7836,144 +7836,144 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C49" t="n">
-        <v>90.53100000000001</v>
+        <v>91.559</v>
       </c>
       <c r="D49" t="n">
-        <v>21.125</v>
+        <v>21.147</v>
       </c>
       <c r="E49" t="n">
-        <v>38.125</v>
+        <v>38.029</v>
       </c>
       <c r="F49" t="n">
-        <v>10.406</v>
+        <v>10.676</v>
       </c>
       <c r="G49" t="n">
-        <v>29.281</v>
+        <v>29.441</v>
       </c>
       <c r="H49" t="n">
-        <v>17.062</v>
+        <v>17.235</v>
       </c>
       <c r="I49" t="n">
-        <v>22.969</v>
+        <v>23.118</v>
       </c>
       <c r="J49" t="n">
-        <v>16.344</v>
+        <v>16.559</v>
       </c>
       <c r="K49" t="n">
-        <v>26.469</v>
+        <v>26.5</v>
       </c>
       <c r="L49" t="n">
-        <v>11.375</v>
+        <v>11.265</v>
       </c>
       <c r="M49" t="n">
-        <v>7.344</v>
+        <v>7.294</v>
       </c>
       <c r="N49" t="n">
-        <v>4.594</v>
+        <v>4.676</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>12.375</v>
+        <v>12.471</v>
       </c>
       <c r="Q49" t="n">
-        <v>11.406</v>
+        <v>11.529</v>
       </c>
       <c r="R49" t="n">
-        <v>23.719</v>
+        <v>23.794</v>
       </c>
       <c r="S49" t="n">
-        <v>21.938</v>
+        <v>22.118</v>
       </c>
       <c r="T49" t="n">
-        <v>3223</v>
+        <v>3474</v>
       </c>
       <c r="U49" t="n">
-        <v>11.312</v>
+        <v>11.588</v>
       </c>
       <c r="V49" t="n">
-        <v>11.219</v>
+        <v>11.176</v>
       </c>
       <c r="W49" t="n">
-        <v>7.188</v>
+        <v>7.441</v>
       </c>
       <c r="X49" t="n">
-        <v>4.156</v>
+        <v>4.382</v>
       </c>
       <c r="Y49" t="n">
-        <v>30.781</v>
+        <v>31.147</v>
       </c>
       <c r="Z49" t="n">
-        <v>43.25</v>
+        <v>43.559</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.712</v>
+        <v>0.715</v>
       </c>
       <c r="AB49" t="n">
-        <v>5</v>
+        <v>4.853</v>
       </c>
       <c r="AC49" t="n">
-        <v>11.469</v>
+        <v>11.294</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.436</v>
+        <v>0.43</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.406</v>
+        <v>2.382</v>
       </c>
       <c r="AF49" t="n">
-        <v>6.375</v>
+        <v>6.294</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.377</v>
+        <v>0.379</v>
       </c>
       <c r="AH49" t="n">
-        <v>3.062</v>
+        <v>3.118</v>
       </c>
       <c r="AI49" t="n">
-        <v>7.188</v>
+        <v>7.118</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.426</v>
+        <v>0.438</v>
       </c>
       <c r="AK49" t="n">
-        <v>7.344</v>
+        <v>7.559</v>
       </c>
       <c r="AL49" t="n">
-        <v>22.094</v>
+        <v>22.324</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.332</v>
+        <v>0.339</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>201:33</t>
+          <t>201:28</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>89.887</v>
+        <v>90.113</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.545</v>
+        <v>0.551</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.584</v>
+        <v>0.59</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.007</v>
+        <v>1.016</v>
       </c>
       <c r="AS49" t="n">
         <v>0.138</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.253</v>
+        <v>0.255</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.321</v>
+        <v>1.328</v>
       </c>
       <c r="AV49" t="n">
         <v>0.2</v>
@@ -7982,7 +7982,7 @@
         <v>0.062</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -7995,144 +7995,144 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C50" t="n">
-        <v>84.09399999999999</v>
+        <v>84.58799999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>21.594</v>
+        <v>21.735</v>
       </c>
       <c r="E50" t="n">
-        <v>42.594</v>
+        <v>42.912</v>
       </c>
       <c r="F50" t="n">
-        <v>7.562</v>
+        <v>7.5</v>
       </c>
       <c r="G50" t="n">
-        <v>23.062</v>
+        <v>22.735</v>
       </c>
       <c r="H50" t="n">
-        <v>18.219</v>
+        <v>18.618</v>
       </c>
       <c r="I50" t="n">
-        <v>24.594</v>
+        <v>25.029</v>
       </c>
       <c r="J50" t="n">
-        <v>15.344</v>
+        <v>15.382</v>
       </c>
       <c r="K50" t="n">
-        <v>25.531</v>
+        <v>25.353</v>
       </c>
       <c r="L50" t="n">
-        <v>11.219</v>
+        <v>11.206</v>
       </c>
       <c r="M50" t="n">
-        <v>6.062</v>
+        <v>6.088</v>
       </c>
       <c r="N50" t="n">
-        <v>4.594</v>
+        <v>4.647</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>13.031</v>
+        <v>13.088</v>
       </c>
       <c r="Q50" t="n">
-        <v>12.125</v>
+        <v>12.176</v>
       </c>
       <c r="R50" t="n">
-        <v>22.406</v>
+        <v>22.618</v>
       </c>
       <c r="S50" t="n">
-        <v>23.625</v>
+        <v>23.735</v>
       </c>
       <c r="T50" t="n">
-        <v>2949</v>
+        <v>3144</v>
       </c>
       <c r="U50" t="n">
-        <v>9.75</v>
+        <v>10.059</v>
       </c>
       <c r="V50" t="n">
-        <v>11.312</v>
+        <v>11.647</v>
       </c>
       <c r="W50" t="n">
-        <v>5.281</v>
+        <v>5.471</v>
       </c>
       <c r="X50" t="n">
-        <v>3.281</v>
+        <v>3.382</v>
       </c>
       <c r="Y50" t="n">
-        <v>31.812</v>
+        <v>32.441</v>
       </c>
       <c r="Z50" t="n">
-        <v>45.656</v>
+        <v>46.618</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.697</v>
+        <v>0.696</v>
       </c>
       <c r="AB50" t="n">
-        <v>5</v>
+        <v>4.882</v>
       </c>
       <c r="AC50" t="n">
-        <v>12.875</v>
+        <v>12.618</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.388</v>
+        <v>0.387</v>
       </c>
       <c r="AE50" t="n">
-        <v>3</v>
+        <v>3.029</v>
       </c>
       <c r="AF50" t="n">
-        <v>8.656000000000001</v>
+        <v>8.706</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.688</v>
+        <v>1.618</v>
       </c>
       <c r="AI50" t="n">
-        <v>4.562</v>
+        <v>4.471</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.37</v>
+        <v>0.362</v>
       </c>
       <c r="AK50" t="n">
-        <v>5.875</v>
+        <v>5.882</v>
       </c>
       <c r="AL50" t="n">
-        <v>18.5</v>
+        <v>18.265</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.318</v>
+        <v>0.322</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>201:33</t>
+          <t>201:28</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>89.509</v>
+        <v>89.748</v>
       </c>
       <c r="AP50" t="n">
         <v>0.502</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.55</v>
+        <v>0.552</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="AS50" t="n">
         <v>0.146</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.277</v>
+        <v>0.284</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.177</v>
+        <v>1.175</v>
       </c>
       <c r="AV50" t="n">
         <v>0.199</v>
@@ -8141,7 +8141,7 @@
         <v>0.061</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.135</v>
+        <v>0.134</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
